--- a/research/traditional_assets/database/data/egypt/egypt_entertainment.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_entertainment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.191733398472343</v>
+        <v>0.1913368733257803</v>
       </c>
       <c r="C2">
-        <v>80.74599602940219</v>
+        <v>80.09603156717944</v>
       </c>
       <c r="D2">
-        <v>57.44599602940219</v>
+        <v>57.60251156717943</v>
       </c>
       <c r="E2">
-        <v>-0.848</v>
+        <v>-0.04152</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.80648</v>
       </c>
       <c r="G2">
         <v>23.3</v>
@@ -1451,28 +1451,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.040565944</v>
       </c>
       <c r="N2">
-        <v>9.789999999999999</v>
+        <v>9.749434055999998</v>
       </c>
       <c r="O2">
-        <v>2.20275</v>
+        <v>2.1936226626</v>
       </c>
       <c r="P2">
-        <v>7.587249999999999</v>
+        <v>7.555811393399999</v>
       </c>
       <c r="Q2">
-        <v>8.997249999999999</v>
+        <v>8.965811393399999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.191733398472343</v>
+        <v>0.192875806389677</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025477611259695</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>241.3354413741733</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1913368733257803</v>
+        <v>0.1909403481792175</v>
       </c>
       <c r="C3">
-        <v>80.09603156717944</v>
+        <v>79.44692230955465</v>
       </c>
       <c r="D3">
-        <v>57.60251156717943</v>
+        <v>57.75988230955465</v>
       </c>
       <c r="E3">
-        <v>-0.04152</v>
+        <v>0.76496</v>
       </c>
       <c r="F3">
-        <v>0.80648</v>
+        <v>1.61296</v>
       </c>
       <c r="G3">
         <v>23.3</v>
@@ -1533,28 +1533,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M3">
-        <v>0.040565944</v>
+        <v>0.081131888</v>
       </c>
       <c r="N3">
-        <v>9.749434055999998</v>
+        <v>9.708868111999999</v>
       </c>
       <c r="O3">
-        <v>2.1936226626</v>
+        <v>2.1844953252</v>
       </c>
       <c r="P3">
-        <v>7.555811393399999</v>
+        <v>7.524372786799999</v>
       </c>
       <c r="Q3">
-        <v>8.965811393399999</v>
+        <v>8.934372786799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.192875806389677</v>
+        <v>0.1940415287543036</v>
       </c>
       <c r="T3">
-        <v>1.025477611259695</v>
+        <v>1.033605543481953</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>241.3354413741733</v>
+        <v>120.6677206870867</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1909403481792175</v>
+        <v>0.1905438230326547</v>
       </c>
       <c r="C4">
-        <v>79.44692230955465</v>
+        <v>78.79867528501694</v>
       </c>
       <c r="D4">
-        <v>57.75988230955465</v>
+        <v>57.91811528501694</v>
       </c>
       <c r="E4">
-        <v>0.76496</v>
+        <v>1.57144</v>
       </c>
       <c r="F4">
-        <v>1.61296</v>
+        <v>2.41944</v>
       </c>
       <c r="G4">
         <v>23.3</v>
@@ -1615,28 +1615,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M4">
-        <v>0.081131888</v>
+        <v>0.121697832</v>
       </c>
       <c r="N4">
-        <v>9.708868111999999</v>
+        <v>9.668302167999999</v>
       </c>
       <c r="O4">
-        <v>2.1844953252</v>
+        <v>2.1753679878</v>
       </c>
       <c r="P4">
-        <v>7.524372786799999</v>
+        <v>7.492934180199999</v>
       </c>
       <c r="Q4">
-        <v>8.934372786799999</v>
+        <v>8.902934180199999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1940415287543036</v>
+        <v>0.1952312866316028</v>
       </c>
       <c r="T4">
-        <v>1.033605543481953</v>
+        <v>1.041901061935598</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>120.6677206870867</v>
+        <v>80.44514712472446</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1905438230326547</v>
+        <v>0.1901472978860919</v>
       </c>
       <c r="C5">
-        <v>78.79867528501694</v>
+        <v>78.15129759928509</v>
       </c>
       <c r="D5">
-        <v>57.91811528501694</v>
+        <v>58.07721759928508</v>
       </c>
       <c r="E5">
-        <v>1.57144</v>
+        <v>2.37792</v>
       </c>
       <c r="F5">
-        <v>2.41944</v>
+        <v>3.22592</v>
       </c>
       <c r="G5">
         <v>23.3</v>
@@ -1697,28 +1697,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M5">
-        <v>0.121697832</v>
+        <v>0.162263776</v>
       </c>
       <c r="N5">
-        <v>9.668302167999999</v>
+        <v>9.627736224</v>
       </c>
       <c r="O5">
-        <v>2.1753679878</v>
+        <v>2.1662406504</v>
       </c>
       <c r="P5">
-        <v>7.492934180199999</v>
+        <v>7.4614955736</v>
       </c>
       <c r="Q5">
-        <v>8.902934180199999</v>
+        <v>8.871495573600001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1952312866316028</v>
+        <v>0.1964458311313458</v>
       </c>
       <c r="T5">
-        <v>1.041901061935598</v>
+        <v>1.05036940369036</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.44514712472446</v>
+        <v>60.33386034354334</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1901472978860919</v>
+        <v>0.1897507727395292</v>
       </c>
       <c r="C6">
-        <v>78.15129759928509</v>
+        <v>77.50479643637118</v>
       </c>
       <c r="D6">
-        <v>58.07721759928508</v>
+        <v>58.23719643637117</v>
       </c>
       <c r="E6">
-        <v>2.37792</v>
+        <v>3.1844</v>
       </c>
       <c r="F6">
-        <v>3.22592</v>
+        <v>4.0324</v>
       </c>
       <c r="G6">
         <v>23.3</v>
@@ -1779,28 +1779,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M6">
-        <v>0.162263776</v>
+        <v>0.20282972</v>
       </c>
       <c r="N6">
-        <v>9.627736224</v>
+        <v>9.587170279999999</v>
       </c>
       <c r="O6">
-        <v>2.1662406504</v>
+        <v>2.157113313</v>
       </c>
       <c r="P6">
-        <v>7.4614955736</v>
+        <v>7.430056966999999</v>
       </c>
       <c r="Q6">
-        <v>8.871495573600001</v>
+        <v>8.840056966999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1964458311313458</v>
+        <v>0.1976859449889781</v>
       </c>
       <c r="T6">
-        <v>1.05036940369036</v>
+        <v>1.05901602632417</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.33386034354334</v>
+        <v>48.26708827483467</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1897507727395292</v>
+        <v>0.1893542475929664</v>
       </c>
       <c r="C7">
-        <v>77.50479643637118</v>
+        <v>76.85917905966194</v>
       </c>
       <c r="D7">
-        <v>58.23719643637117</v>
+        <v>58.39805905966194</v>
       </c>
       <c r="E7">
-        <v>3.1844</v>
+        <v>3.990880000000001</v>
       </c>
       <c r="F7">
-        <v>4.0324</v>
+        <v>4.838880000000001</v>
       </c>
       <c r="G7">
         <v>23.3</v>
@@ -1861,28 +1861,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M7">
-        <v>0.20282972</v>
+        <v>0.243395664</v>
       </c>
       <c r="N7">
-        <v>9.587170279999999</v>
+        <v>9.546604336</v>
       </c>
       <c r="O7">
-        <v>2.157113313</v>
+        <v>2.1479859756</v>
       </c>
       <c r="P7">
-        <v>7.430056966999999</v>
+        <v>7.3986183604</v>
       </c>
       <c r="Q7">
-        <v>8.840056966999999</v>
+        <v>8.808618360400001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1976859449889781</v>
+        <v>0.1989524442478366</v>
       </c>
       <c r="T7">
-        <v>1.05901602632417</v>
+        <v>1.067846619652316</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.26708827483467</v>
+        <v>40.22257356236223</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1893542475929664</v>
+        <v>0.1889577224464036</v>
       </c>
       <c r="C8">
-        <v>76.85917905966194</v>
+        <v>76.21445281301803</v>
       </c>
       <c r="D8">
-        <v>58.39805905966194</v>
+        <v>58.55981281301803</v>
       </c>
       <c r="E8">
-        <v>3.99088</v>
+        <v>4.797359999999999</v>
       </c>
       <c r="F8">
-        <v>4.83888</v>
+        <v>5.645359999999999</v>
       </c>
       <c r="G8">
         <v>23.3</v>
@@ -1943,28 +1943,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M8">
-        <v>0.243395664</v>
+        <v>0.283961608</v>
       </c>
       <c r="N8">
-        <v>9.546604336</v>
+        <v>9.506038391999999</v>
       </c>
       <c r="O8">
-        <v>2.1479859756</v>
+        <v>2.1388586382</v>
       </c>
       <c r="P8">
-        <v>7.3986183604</v>
+        <v>7.367179753799999</v>
       </c>
       <c r="Q8">
-        <v>8.808618360400001</v>
+        <v>8.777179753799999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1989524442478366</v>
+        <v>0.2002461800498964</v>
       </c>
       <c r="T8">
-        <v>1.067846619652316</v>
+        <v>1.076867118213326</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.22257356236224</v>
+        <v>34.47649162488191</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1889577224464036</v>
+        <v>0.1885611972998409</v>
       </c>
       <c r="C9">
-        <v>76.21445281301803</v>
+        <v>75.57062512189157</v>
       </c>
       <c r="D9">
-        <v>58.55981281301803</v>
+        <v>58.72246512189157</v>
       </c>
       <c r="E9">
-        <v>4.79736</v>
+        <v>5.60384</v>
       </c>
       <c r="F9">
-        <v>5.64536</v>
+        <v>6.45184</v>
       </c>
       <c r="G9">
         <v>23.3</v>
@@ -2025,28 +2025,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M9">
-        <v>0.283961608</v>
+        <v>0.324527552</v>
       </c>
       <c r="N9">
-        <v>9.506038391999999</v>
+        <v>9.465472448</v>
       </c>
       <c r="O9">
-        <v>2.1388586382</v>
+        <v>2.1297313008</v>
       </c>
       <c r="P9">
-        <v>7.367179753799999</v>
+        <v>7.3357411472</v>
       </c>
       <c r="Q9">
-        <v>8.777179753799999</v>
+        <v>8.7457411472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2002461800498964</v>
+        <v>0.2015680405433053</v>
       </c>
       <c r="T9">
-        <v>1.076867118213326</v>
+        <v>1.08608371456914</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.47649162488191</v>
+        <v>30.16693017177167</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1885611972998409</v>
+        <v>0.1881646721532781</v>
       </c>
       <c r="C10">
-        <v>75.57062512189157</v>
+        <v>74.92770349446249</v>
       </c>
       <c r="D10">
-        <v>58.72246512189157</v>
+        <v>58.88602349446248</v>
       </c>
       <c r="E10">
-        <v>5.60384</v>
+        <v>6.41032</v>
       </c>
       <c r="F10">
-        <v>6.45184</v>
+        <v>7.258319999999999</v>
       </c>
       <c r="G10">
         <v>23.3</v>
@@ -2107,28 +2107,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M10">
-        <v>0.324527552</v>
+        <v>0.365093496</v>
       </c>
       <c r="N10">
-        <v>9.465472448</v>
+        <v>9.424906503999999</v>
       </c>
       <c r="O10">
-        <v>2.1297313008</v>
+        <v>2.1206039634</v>
       </c>
       <c r="P10">
-        <v>7.3357411472</v>
+        <v>7.304302540599999</v>
       </c>
       <c r="Q10">
-        <v>8.7457411472</v>
+        <v>8.714302540599999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2015680405433053</v>
+        <v>0.2029189529156902</v>
       </c>
       <c r="T10">
-        <v>1.08608371456914</v>
+        <v>1.095502873482225</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.16693017177167</v>
+        <v>26.81504904157482</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1881646721532781</v>
+        <v>0.1877681470067153</v>
       </c>
       <c r="C11">
-        <v>74.92770349446249</v>
+        <v>74.28569552279387</v>
       </c>
       <c r="D11">
-        <v>58.88602349446248</v>
+        <v>59.05049552279388</v>
       </c>
       <c r="E11">
-        <v>6.41032</v>
+        <v>7.216799999999998</v>
       </c>
       <c r="F11">
-        <v>7.258319999999999</v>
+        <v>8.064799999999998</v>
       </c>
       <c r="G11">
         <v>23.3</v>
@@ -2189,28 +2189,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M11">
-        <v>0.365093496</v>
+        <v>0.4056594399999999</v>
       </c>
       <c r="N11">
-        <v>9.424906503999999</v>
+        <v>9.38434056</v>
       </c>
       <c r="O11">
-        <v>2.1206039634</v>
+        <v>2.111476626</v>
       </c>
       <c r="P11">
-        <v>7.304302540599999</v>
+        <v>7.272863934</v>
       </c>
       <c r="Q11">
-        <v>8.714302540599999</v>
+        <v>8.682863934</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2029189529156902</v>
+        <v>0.204299885563017</v>
       </c>
       <c r="T11">
-        <v>1.095502873482225</v>
+        <v>1.105131347037822</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.81504904157482</v>
+        <v>24.13354413741735</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1877681470067153</v>
+        <v>0.1873716218601525</v>
       </c>
       <c r="C12">
-        <v>74.28569552279387</v>
+        <v>73.64460888400654</v>
       </c>
       <c r="D12">
-        <v>59.05049552279388</v>
+        <v>59.21588888400655</v>
       </c>
       <c r="E12">
-        <v>7.2168</v>
+        <v>8.02328</v>
       </c>
       <c r="F12">
-        <v>8.0648</v>
+        <v>8.87128</v>
       </c>
       <c r="G12">
         <v>23.3</v>
@@ -2271,28 +2271,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M12">
-        <v>0.40565944</v>
+        <v>0.446225384</v>
       </c>
       <c r="N12">
-        <v>9.384340559999998</v>
+        <v>9.343774615999999</v>
       </c>
       <c r="O12">
-        <v>2.111476626</v>
+        <v>2.1023492886</v>
       </c>
       <c r="P12">
-        <v>7.272863933999998</v>
+        <v>7.2414253274</v>
       </c>
       <c r="Q12">
-        <v>8.682863933999998</v>
+        <v>8.6514253274</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.204299885563017</v>
+        <v>0.2057118504046658</v>
       </c>
       <c r="T12">
-        <v>1.105131347037822</v>
+        <v>1.114976190785681</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.13354413741733</v>
+        <v>21.9395855794703</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1873716218601525</v>
+        <v>0.1869750967135898</v>
       </c>
       <c r="C13">
-        <v>73.64460888400654</v>
+        <v>73.00445134147375</v>
       </c>
       <c r="D13">
-        <v>59.21588888400655</v>
+        <v>59.38221134147376</v>
       </c>
       <c r="E13">
-        <v>8.02328</v>
+        <v>8.829759999999998</v>
       </c>
       <c r="F13">
-        <v>8.87128</v>
+        <v>9.677759999999999</v>
       </c>
       <c r="G13">
         <v>23.3</v>
@@ -2353,28 +2353,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M13">
-        <v>0.446225384</v>
+        <v>0.4867913279999999</v>
       </c>
       <c r="N13">
-        <v>9.343774615999999</v>
+        <v>9.303208671999998</v>
       </c>
       <c r="O13">
-        <v>2.1023492886</v>
+        <v>2.0932219512</v>
       </c>
       <c r="P13">
-        <v>7.2414253274</v>
+        <v>7.209986720799998</v>
       </c>
       <c r="Q13">
-        <v>8.6514253274</v>
+        <v>8.619986720799998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2057118504046658</v>
+        <v>0.207155905356352</v>
       </c>
       <c r="T13">
-        <v>1.114976190785681</v>
+        <v>1.125044780982354</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.9395855794703</v>
+        <v>20.11128678118111</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1869750967135898</v>
+        <v>0.186578571567027</v>
       </c>
       <c r="C14">
-        <v>73.00445134147375</v>
+        <v>72.36523074603583</v>
       </c>
       <c r="D14">
-        <v>59.38221134147376</v>
+        <v>59.54947074603583</v>
       </c>
       <c r="E14">
-        <v>8.829759999999998</v>
+        <v>9.636239999999999</v>
       </c>
       <c r="F14">
-        <v>9.677759999999999</v>
+        <v>10.48424</v>
       </c>
       <c r="G14">
         <v>23.3</v>
@@ -2435,28 +2435,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M14">
-        <v>0.4867913279999999</v>
+        <v>0.5273572719999999</v>
       </c>
       <c r="N14">
-        <v>9.303208671999998</v>
+        <v>9.262642727999999</v>
       </c>
       <c r="O14">
-        <v>2.0932219512</v>
+        <v>2.0840946138</v>
       </c>
       <c r="P14">
-        <v>7.209986720799998</v>
+        <v>7.1785481142</v>
       </c>
       <c r="Q14">
-        <v>8.619986720799998</v>
+        <v>8.5885481142</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.207155905356352</v>
+        <v>0.2086331569735943</v>
       </c>
       <c r="T14">
-        <v>1.125044780982354</v>
+        <v>1.135344833022629</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.11128678118111</v>
+        <v>18.56426472109026</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.186578571567027</v>
+        <v>0.1861820464204642</v>
       </c>
       <c r="C15">
-        <v>72.36523074603583</v>
+        <v>71.72695503723546</v>
       </c>
       <c r="D15">
-        <v>59.54947074603583</v>
+        <v>59.71767503723547</v>
       </c>
       <c r="E15">
-        <v>9.636239999999999</v>
+        <v>10.44272</v>
       </c>
       <c r="F15">
-        <v>10.48424</v>
+        <v>11.29072</v>
       </c>
       <c r="G15">
         <v>23.3</v>
@@ -2517,28 +2517,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M15">
-        <v>0.5273572719999999</v>
+        <v>0.567923216</v>
       </c>
       <c r="N15">
-        <v>9.262642727999999</v>
+        <v>9.222076783999999</v>
       </c>
       <c r="O15">
-        <v>2.0840946138</v>
+        <v>2.0749672764</v>
       </c>
       <c r="P15">
-        <v>7.1785481142</v>
+        <v>7.147109507599999</v>
       </c>
       <c r="Q15">
-        <v>8.5885481142</v>
+        <v>8.5571095076</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2086331569735943</v>
+        <v>0.2101447632796095</v>
       </c>
       <c r="T15">
-        <v>1.135344833022629</v>
+        <v>1.145884421156864</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.56426472109026</v>
+        <v>17.23824581244095</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1861820464204642</v>
+        <v>0.1857855212739014</v>
       </c>
       <c r="C16">
-        <v>71.72695503723546</v>
+        <v>71.08963224457403</v>
       </c>
       <c r="D16">
-        <v>59.71767503723547</v>
+        <v>59.88683224457404</v>
       </c>
       <c r="E16">
-        <v>10.44272</v>
+        <v>11.2492</v>
       </c>
       <c r="F16">
-        <v>11.29072</v>
+        <v>12.0972</v>
       </c>
       <c r="G16">
         <v>23.3</v>
@@ -2599,28 +2599,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M16">
-        <v>0.567923216</v>
+        <v>0.60848916</v>
       </c>
       <c r="N16">
-        <v>9.222076783999999</v>
+        <v>9.18151084</v>
       </c>
       <c r="O16">
-        <v>2.0749672764</v>
+        <v>2.065839939</v>
       </c>
       <c r="P16">
-        <v>7.147109507599999</v>
+        <v>7.115670901</v>
       </c>
       <c r="Q16">
-        <v>8.5571095076</v>
+        <v>8.525670901</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2101447632796095</v>
+        <v>0.2116919367928252</v>
       </c>
       <c r="T16">
-        <v>1.145884421156864</v>
+        <v>1.15667199960014</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.23824581244095</v>
+        <v>16.08902942494489</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1857855212739014</v>
+        <v>0.1853889961273387</v>
       </c>
       <c r="C17">
-        <v>71.08963224457403</v>
+        <v>70.45327048878936</v>
       </c>
       <c r="D17">
-        <v>59.88683224457404</v>
+        <v>60.05695048878935</v>
       </c>
       <c r="E17">
-        <v>11.2492</v>
+        <v>12.05568</v>
       </c>
       <c r="F17">
-        <v>12.0972</v>
+        <v>12.90368</v>
       </c>
       <c r="G17">
         <v>23.3</v>
@@ -2681,28 +2681,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M17">
-        <v>0.60848916</v>
+        <v>0.649055104</v>
       </c>
       <c r="N17">
-        <v>9.18151084</v>
+        <v>9.140944895999999</v>
       </c>
       <c r="O17">
-        <v>2.065839939</v>
+        <v>2.0567126016</v>
       </c>
       <c r="P17">
-        <v>7.115670901</v>
+        <v>7.0842322944</v>
       </c>
       <c r="Q17">
-        <v>8.525670901</v>
+        <v>8.4942322944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2116919367928252</v>
+        <v>0.2132759477706413</v>
       </c>
       <c r="T17">
-        <v>1.15667199960014</v>
+        <v>1.167716425149208</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.08902942494489</v>
+        <v>15.08346508588583</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1853889961273387</v>
+        <v>0.1849924709807759</v>
       </c>
       <c r="C18">
-        <v>70.45327048878936</v>
+        <v>69.81787798315509</v>
       </c>
       <c r="D18">
-        <v>60.05695048878935</v>
+        <v>60.22803798315509</v>
       </c>
       <c r="E18">
-        <v>12.05568</v>
+        <v>12.86216</v>
       </c>
       <c r="F18">
-        <v>12.90368</v>
+        <v>13.71016</v>
       </c>
       <c r="G18">
         <v>23.3</v>
@@ -2763,28 +2763,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M18">
-        <v>0.649055104</v>
+        <v>0.689621048</v>
       </c>
       <c r="N18">
-        <v>9.140944895999999</v>
+        <v>9.100378952</v>
       </c>
       <c r="O18">
-        <v>2.0567126016</v>
+        <v>2.0475852642</v>
       </c>
       <c r="P18">
-        <v>7.0842322944</v>
+        <v>7.052793687799999</v>
       </c>
       <c r="Q18">
-        <v>8.4942322944</v>
+        <v>8.4627936878</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2132759477706413</v>
+        <v>0.2148981276876818</v>
       </c>
       <c r="T18">
-        <v>1.167716425149208</v>
+        <v>1.179026981434398</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.08346508588583</v>
+        <v>14.1962024337749</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1849924709807759</v>
+        <v>0.1845959458342131</v>
       </c>
       <c r="C19">
-        <v>69.81787798315509</v>
+        <v>69.18346303480284</v>
       </c>
       <c r="D19">
-        <v>60.22803798315509</v>
+        <v>60.40010303480283</v>
       </c>
       <c r="E19">
-        <v>12.86216</v>
+        <v>13.66864</v>
       </c>
       <c r="F19">
-        <v>13.71016</v>
+        <v>14.51664</v>
       </c>
       <c r="G19">
         <v>23.3</v>
@@ -2845,28 +2845,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M19">
-        <v>0.689621048</v>
+        <v>0.730186992</v>
       </c>
       <c r="N19">
-        <v>9.100378952</v>
+        <v>9.059813007999999</v>
       </c>
       <c r="O19">
-        <v>2.0475852642</v>
+        <v>2.0384579268</v>
       </c>
       <c r="P19">
-        <v>7.052793687799999</v>
+        <v>7.021355081199999</v>
       </c>
       <c r="Q19">
-        <v>8.4627936878</v>
+        <v>8.4313550812</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2148981276876818</v>
+        <v>0.2165598729685526</v>
       </c>
       <c r="T19">
-        <v>1.179026981434398</v>
+        <v>1.190613404946057</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.1962024337749</v>
+        <v>13.40752452078741</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1845959458342132</v>
+        <v>0.1844202956876504</v>
       </c>
       <c r="C20">
-        <v>69.18346303480283</v>
+        <v>68.45351790942445</v>
       </c>
       <c r="D20">
-        <v>60.40010303480283</v>
+        <v>60.47663790942445</v>
       </c>
       <c r="E20">
-        <v>13.66864</v>
+        <v>14.47512</v>
       </c>
       <c r="F20">
-        <v>14.51664</v>
+        <v>15.32312</v>
       </c>
       <c r="G20">
         <v>23.3</v>
@@ -2927,45 +2927,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M20">
-        <v>0.7301869919999999</v>
+        <v>0.7937376159999999</v>
       </c>
       <c r="N20">
-        <v>9.059813007999999</v>
+        <v>8.996262384</v>
       </c>
       <c r="O20">
-        <v>2.0384579268</v>
+        <v>2.0241590364</v>
       </c>
       <c r="P20">
-        <v>7.021355081199999</v>
+        <v>6.972103347599999</v>
       </c>
       <c r="Q20">
-        <v>8.4313550812</v>
+        <v>8.382103347599999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2165598729685526</v>
+        <v>0.2182626489970992</v>
       </c>
       <c r="T20">
-        <v>1.190613404946057</v>
+        <v>1.202485912988867</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.225</v>
       </c>
       <c r="W20">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.40752452078741</v>
+        <v>12.33405070221593</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1844202956876504</v>
+        <v>0.1840353955410876</v>
       </c>
       <c r="C21">
-        <v>68.45351790942445</v>
+        <v>67.81542797120166</v>
       </c>
       <c r="D21">
-        <v>60.47663790942445</v>
+        <v>60.64502797120166</v>
       </c>
       <c r="E21">
-        <v>14.47512</v>
+        <v>15.2816</v>
       </c>
       <c r="F21">
-        <v>15.32312</v>
+        <v>16.1296</v>
       </c>
       <c r="G21">
         <v>23.3</v>
@@ -3009,28 +3009,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M21">
-        <v>0.7937376159999999</v>
+        <v>0.83551328</v>
       </c>
       <c r="N21">
-        <v>8.996262384</v>
+        <v>8.954486719999998</v>
       </c>
       <c r="O21">
-        <v>2.0241590364</v>
+        <v>2.014759512</v>
       </c>
       <c r="P21">
-        <v>6.972103347599999</v>
+        <v>6.939727207999999</v>
       </c>
       <c r="Q21">
-        <v>8.382103347599999</v>
+        <v>8.349727207999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2182626489970992</v>
+        <v>0.2200079944263595</v>
       </c>
       <c r="T21">
-        <v>1.202485912988867</v>
+        <v>1.214655233732747</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.33405070221593</v>
+        <v>11.71734816710513</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1840353955410876</v>
+        <v>0.1836504953945249</v>
       </c>
       <c r="C22">
-        <v>67.81542797120166</v>
+        <v>67.17827837576505</v>
       </c>
       <c r="D22">
-        <v>60.64502797120166</v>
+        <v>60.81435837576505</v>
       </c>
       <c r="E22">
-        <v>15.2816</v>
+        <v>16.08808</v>
       </c>
       <c r="F22">
-        <v>16.1296</v>
+        <v>16.93608</v>
       </c>
       <c r="G22">
         <v>23.3</v>
@@ -3091,28 +3091,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M22">
-        <v>0.83551328</v>
+        <v>0.877288944</v>
       </c>
       <c r="N22">
-        <v>8.954486719999998</v>
+        <v>8.912711055999999</v>
       </c>
       <c r="O22">
-        <v>2.014759512</v>
+        <v>2.0053599876</v>
       </c>
       <c r="P22">
-        <v>6.939727207999999</v>
+        <v>6.907351068399999</v>
       </c>
       <c r="Q22">
-        <v>8.349727207999999</v>
+        <v>8.317351068399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2200079944263595</v>
+        <v>0.2217975258158542</v>
       </c>
       <c r="T22">
-        <v>1.214655233732747</v>
+        <v>1.227132638546093</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.71734816710513</v>
+        <v>11.1593792067668</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1836504953945249</v>
+        <v>0.1832655952479621</v>
       </c>
       <c r="C23">
-        <v>67.17827837576505</v>
+        <v>66.54207702192181</v>
       </c>
       <c r="D23">
-        <v>60.81435837576505</v>
+        <v>60.98463702192181</v>
       </c>
       <c r="E23">
-        <v>16.08808</v>
+        <v>16.89456</v>
       </c>
       <c r="F23">
-        <v>16.93608</v>
+        <v>17.74256</v>
       </c>
       <c r="G23">
         <v>23.3</v>
@@ -3173,28 +3173,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M23">
-        <v>0.8772889439999998</v>
+        <v>0.919064608</v>
       </c>
       <c r="N23">
-        <v>8.912711055999999</v>
+        <v>8.870935392</v>
       </c>
       <c r="O23">
-        <v>2.0053599876</v>
+        <v>1.9959604632</v>
       </c>
       <c r="P23">
-        <v>6.907351068399999</v>
+        <v>6.874974928799999</v>
       </c>
       <c r="Q23">
-        <v>8.317351068399999</v>
+        <v>8.284974928800001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2217975258158542</v>
+        <v>0.2236329426255924</v>
       </c>
       <c r="T23">
-        <v>1.227132638546093</v>
+        <v>1.239929976816192</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.1593792067668</v>
+        <v>10.65213469736831</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1832655952479621</v>
+        <v>0.1828806951013993</v>
       </c>
       <c r="C24">
-        <v>66.54207702192181</v>
+        <v>65.90683189719327</v>
       </c>
       <c r="D24">
-        <v>60.98463702192181</v>
+        <v>61.15587189719328</v>
       </c>
       <c r="E24">
-        <v>16.89456</v>
+        <v>17.70104</v>
       </c>
       <c r="F24">
-        <v>17.74256</v>
+        <v>18.54904</v>
       </c>
       <c r="G24">
         <v>23.3</v>
@@ -3255,28 +3255,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M24">
-        <v>0.919064608</v>
+        <v>0.9608402720000001</v>
       </c>
       <c r="N24">
-        <v>8.870935392</v>
+        <v>8.829159727999999</v>
       </c>
       <c r="O24">
-        <v>1.9959604632</v>
+        <v>1.9865609388</v>
       </c>
       <c r="P24">
-        <v>6.874974928799999</v>
+        <v>6.842598789199998</v>
       </c>
       <c r="Q24">
-        <v>8.284974928800001</v>
+        <v>8.252598789199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2236329426255924</v>
+        <v>0.2255160325992198</v>
       </c>
       <c r="T24">
-        <v>1.239929976816192</v>
+        <v>1.253059713482916</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.65213469736831</v>
+        <v>10.18899840617838</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1828806951013993</v>
+        <v>0.1828119949548365</v>
       </c>
       <c r="C25">
-        <v>65.90683189719327</v>
+        <v>65.13101649239093</v>
       </c>
       <c r="D25">
-        <v>61.15587189719328</v>
+        <v>61.18653649239092</v>
       </c>
       <c r="E25">
-        <v>17.70104</v>
+        <v>18.50752</v>
       </c>
       <c r="F25">
-        <v>18.54904</v>
+        <v>19.35552</v>
       </c>
       <c r="G25">
         <v>23.3</v>
@@ -3337,45 +3337,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M25">
-        <v>0.9608402720000001</v>
+        <v>1.03552032</v>
       </c>
       <c r="N25">
-        <v>8.829159727999999</v>
+        <v>8.754479679999999</v>
       </c>
       <c r="O25">
-        <v>1.9865609388</v>
+        <v>1.969757928</v>
       </c>
       <c r="P25">
-        <v>6.842598789199998</v>
+        <v>6.784721751999999</v>
       </c>
       <c r="Q25">
-        <v>8.252598789199999</v>
+        <v>8.194721752</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2255160325992198</v>
+        <v>0.2274486775721533</v>
       </c>
       <c r="T25">
-        <v>1.253059713482916</v>
+        <v>1.266534969535607</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.225</v>
       </c>
       <c r="W25">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.18899840617838</v>
+        <v>9.454184346667382</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1828119949548365</v>
+        <v>0.1824402698082737</v>
       </c>
       <c r="C26">
-        <v>65.13101649239093</v>
+        <v>64.49099235695573</v>
       </c>
       <c r="D26">
-        <v>61.18653649239092</v>
+        <v>61.35299235695572</v>
       </c>
       <c r="E26">
-        <v>18.50752</v>
+        <v>19.314</v>
       </c>
       <c r="F26">
-        <v>19.35552</v>
+        <v>20.162</v>
       </c>
       <c r="G26">
         <v>23.3</v>
@@ -3419,28 +3419,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M26">
-        <v>1.03552032</v>
+        <v>1.078667</v>
       </c>
       <c r="N26">
-        <v>8.754479679999999</v>
+        <v>8.711333</v>
       </c>
       <c r="O26">
-        <v>1.969757928</v>
+        <v>1.960049925</v>
       </c>
       <c r="P26">
-        <v>6.784721751999999</v>
+        <v>6.751283075</v>
       </c>
       <c r="Q26">
-        <v>8.194721752</v>
+        <v>8.161283075</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2274486775721533</v>
+        <v>0.229432859744365</v>
       </c>
       <c r="T26">
-        <v>1.266534969535607</v>
+        <v>1.280369565749702</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.454184346667384</v>
+        <v>9.076016972800689</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1824402698082737</v>
+        <v>0.182068544661711</v>
       </c>
       <c r="C27">
-        <v>64.49099235695573</v>
+        <v>63.85187636698878</v>
       </c>
       <c r="D27">
-        <v>61.35299235695572</v>
+        <v>61.52035636698878</v>
       </c>
       <c r="E27">
-        <v>19.314</v>
+        <v>20.12048</v>
       </c>
       <c r="F27">
-        <v>20.162</v>
+        <v>20.96848</v>
       </c>
       <c r="G27">
         <v>23.3</v>
@@ -3501,28 +3501,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M27">
-        <v>1.078667</v>
+        <v>1.12181368</v>
       </c>
       <c r="N27">
-        <v>8.711333</v>
+        <v>8.668186319999998</v>
       </c>
       <c r="O27">
-        <v>1.960049925</v>
+        <v>1.950341922</v>
       </c>
       <c r="P27">
-        <v>6.751283075</v>
+        <v>6.717844397999999</v>
       </c>
       <c r="Q27">
-        <v>8.161283075</v>
+        <v>8.127844397999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.229432859744365</v>
+        <v>0.2314706684617716</v>
       </c>
       <c r="T27">
-        <v>1.280369565749702</v>
+        <v>1.294578069969585</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.076016972800689</v>
+        <v>8.726939396923736</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.182068544661711</v>
+        <v>0.1816968195151482</v>
       </c>
       <c r="C28">
-        <v>63.85187636698878</v>
+        <v>63.21367597477286</v>
       </c>
       <c r="D28">
-        <v>61.52035636698878</v>
+        <v>61.68863597477286</v>
       </c>
       <c r="E28">
-        <v>20.12048</v>
+        <v>20.92696</v>
       </c>
       <c r="F28">
-        <v>20.96848</v>
+        <v>21.77496</v>
       </c>
       <c r="G28">
         <v>23.3</v>
@@ -3583,28 +3583,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M28">
-        <v>1.12181368</v>
+        <v>1.16496036</v>
       </c>
       <c r="N28">
-        <v>8.668186319999998</v>
+        <v>8.625039639999999</v>
       </c>
       <c r="O28">
-        <v>1.950341922</v>
+        <v>1.940633919</v>
       </c>
       <c r="P28">
-        <v>6.717844397999999</v>
+        <v>6.684405720999999</v>
       </c>
       <c r="Q28">
-        <v>8.127844397999999</v>
+        <v>8.094405720999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2314706684617716</v>
+        <v>0.2335643075549975</v>
       </c>
       <c r="T28">
-        <v>1.294578069969585</v>
+        <v>1.309175848277683</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.726939396923736</v>
+        <v>8.403719419259897</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1816968195151482</v>
+        <v>0.1813250943685854</v>
       </c>
       <c r="C29">
-        <v>63.21367597477286</v>
+        <v>62.57639871435269</v>
       </c>
       <c r="D29">
-        <v>61.68863597477286</v>
+        <v>61.85783871435269</v>
       </c>
       <c r="E29">
-        <v>20.92696</v>
+        <v>21.73344</v>
       </c>
       <c r="F29">
-        <v>21.77496</v>
+        <v>22.58144</v>
       </c>
       <c r="G29">
         <v>23.3</v>
@@ -3665,28 +3665,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M29">
-        <v>1.16496036</v>
+        <v>1.20810704</v>
       </c>
       <c r="N29">
-        <v>8.625039639999999</v>
+        <v>8.581892959999999</v>
       </c>
       <c r="O29">
-        <v>1.940633919</v>
+        <v>1.930925916</v>
       </c>
       <c r="P29">
-        <v>6.684405720999999</v>
+        <v>6.650967044</v>
       </c>
       <c r="Q29">
-        <v>8.094405720999999</v>
+        <v>8.060967044</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2335643075549975</v>
+        <v>0.235716103289702</v>
       </c>
       <c r="T29">
-        <v>1.309175848277683</v>
+        <v>1.324179120427672</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.403719419259897</v>
+        <v>8.103586582857757</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1813250943685854</v>
+        <v>0.1809533692220227</v>
       </c>
       <c r="C30">
-        <v>62.57639871435269</v>
+        <v>61.94005220265941</v>
       </c>
       <c r="D30">
-        <v>61.85783871435269</v>
+        <v>62.02797220265941</v>
       </c>
       <c r="E30">
-        <v>21.73344</v>
+        <v>22.53992</v>
       </c>
       <c r="F30">
-        <v>22.58144</v>
+        <v>23.38792</v>
       </c>
       <c r="G30">
         <v>23.3</v>
@@ -3747,28 +3747,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M30">
-        <v>1.20810704</v>
+        <v>1.25125372</v>
       </c>
       <c r="N30">
-        <v>8.581892959999999</v>
+        <v>8.53874628</v>
       </c>
       <c r="O30">
-        <v>1.930925916</v>
+        <v>1.921217913</v>
       </c>
       <c r="P30">
-        <v>6.650967044</v>
+        <v>6.617528367</v>
       </c>
       <c r="Q30">
-        <v>8.060967044</v>
+        <v>8.027528367</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.235716103289702</v>
+        <v>0.2379285129887644</v>
       </c>
       <c r="T30">
-        <v>1.324179120427672</v>
+        <v>1.339605019962169</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.103586582857757</v>
+        <v>7.824152562759214</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1809533692220227</v>
+        <v>0.1807676440754599</v>
       </c>
       <c r="C31">
-        <v>61.94005220265943</v>
+        <v>61.21892713574167</v>
       </c>
       <c r="D31">
-        <v>62.02797220265942</v>
+        <v>62.11332713574167</v>
       </c>
       <c r="E31">
-        <v>22.53992</v>
+        <v>23.3464</v>
       </c>
       <c r="F31">
-        <v>23.38792</v>
+        <v>24.1944</v>
       </c>
       <c r="G31">
         <v>23.3</v>
@@ -3829,45 +3829,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M31">
-        <v>1.25125372</v>
+        <v>1.31375592</v>
       </c>
       <c r="N31">
-        <v>8.53874628</v>
+        <v>8.476244079999999</v>
       </c>
       <c r="O31">
-        <v>1.921217913</v>
+        <v>1.907154918</v>
       </c>
       <c r="P31">
-        <v>6.617528367</v>
+        <v>6.569089161999999</v>
       </c>
       <c r="Q31">
-        <v>8.027528367</v>
+        <v>7.979089161999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2379285129887643</v>
+        <v>0.2402041343935141</v>
       </c>
       <c r="T31">
-        <v>1.339605019962169</v>
+        <v>1.355471659483365</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.225</v>
       </c>
       <c r="W31">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.824152562759215</v>
+        <v>7.451916943597864</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1807676440754599</v>
+        <v>0.1804021189288971</v>
       </c>
       <c r="C32">
-        <v>61.21892713574167</v>
+        <v>60.58112191727901</v>
       </c>
       <c r="D32">
-        <v>62.11332713574167</v>
+        <v>62.282001917279</v>
       </c>
       <c r="E32">
-        <v>23.3464</v>
+        <v>24.15288</v>
       </c>
       <c r="F32">
-        <v>24.1944</v>
+        <v>25.00088</v>
       </c>
       <c r="G32">
         <v>23.3</v>
@@ -3911,28 +3911,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M32">
-        <v>1.31375592</v>
+        <v>1.357547784</v>
       </c>
       <c r="N32">
-        <v>8.476244079999999</v>
+        <v>8.432452216</v>
       </c>
       <c r="O32">
-        <v>1.907154918</v>
+        <v>1.8973017486</v>
       </c>
       <c r="P32">
-        <v>6.569089161999999</v>
+        <v>6.535150467399999</v>
       </c>
       <c r="Q32">
-        <v>7.979089161999999</v>
+        <v>7.9451504674</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2402041343935141</v>
+        <v>0.2425457158389813</v>
       </c>
       <c r="T32">
-        <v>1.355471659483365</v>
+        <v>1.371798201599379</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.451916943597864</v>
+        <v>7.21153252606245</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1804021189288971</v>
+        <v>0.1800365937823343</v>
       </c>
       <c r="C33">
-        <v>60.58112191727901</v>
+        <v>59.94423529891644</v>
       </c>
       <c r="D33">
-        <v>62.282001917279</v>
+        <v>62.45159529891644</v>
       </c>
       <c r="E33">
-        <v>24.15288</v>
+        <v>24.95936</v>
       </c>
       <c r="F33">
-        <v>25.00088</v>
+        <v>25.80736</v>
       </c>
       <c r="G33">
         <v>23.3</v>
@@ -3993,28 +3993,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M33">
-        <v>1.357547784</v>
+        <v>1.401339648</v>
       </c>
       <c r="N33">
-        <v>8.432452216</v>
+        <v>8.388660351999999</v>
       </c>
       <c r="O33">
-        <v>1.8973017486</v>
+        <v>1.8874485792</v>
       </c>
       <c r="P33">
-        <v>6.535150467399999</v>
+        <v>6.501211772799999</v>
       </c>
       <c r="Q33">
-        <v>7.9451504674</v>
+        <v>7.911211772799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2425457158389813</v>
+        <v>0.2449561673269623</v>
       </c>
       <c r="T33">
-        <v>1.371798201599379</v>
+        <v>1.388604936130569</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.21153252606245</v>
+        <v>6.986172134622997</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1800365937823343</v>
+        <v>0.1796710686357716</v>
       </c>
       <c r="C34">
-        <v>59.94423529891644</v>
+        <v>59.3082748051648</v>
       </c>
       <c r="D34">
-        <v>62.45159529891644</v>
+        <v>62.6221148051648</v>
       </c>
       <c r="E34">
-        <v>24.95936</v>
+        <v>25.76584</v>
       </c>
       <c r="F34">
-        <v>25.80736</v>
+        <v>26.61384</v>
       </c>
       <c r="G34">
         <v>23.3</v>
@@ -4075,28 +4075,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M34">
-        <v>1.401339648</v>
+        <v>1.445131512</v>
       </c>
       <c r="N34">
-        <v>8.388660351999999</v>
+        <v>8.344868487999999</v>
       </c>
       <c r="O34">
-        <v>1.8874485792</v>
+        <v>1.8775954098</v>
       </c>
       <c r="P34">
-        <v>6.501211772799999</v>
+        <v>6.4672730782</v>
       </c>
       <c r="Q34">
-        <v>7.911211772799999</v>
+        <v>7.8772730782</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2449561673269623</v>
+        <v>0.2474385725907039</v>
       </c>
       <c r="T34">
-        <v>1.388604936130569</v>
+        <v>1.405913364229855</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.986172134622997</v>
+        <v>6.77446994872533</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1796710686357716</v>
+        <v>0.1793055434892088</v>
       </c>
       <c r="C35">
-        <v>59.3082748051648</v>
+        <v>58.67324804294051</v>
       </c>
       <c r="D35">
-        <v>62.6221148051648</v>
+        <v>62.79356804294052</v>
       </c>
       <c r="E35">
-        <v>25.76584</v>
+        <v>26.57232</v>
       </c>
       <c r="F35">
-        <v>26.61384</v>
+        <v>27.42032</v>
       </c>
       <c r="G35">
         <v>23.3</v>
@@ -4157,28 +4157,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M35">
-        <v>1.445131512</v>
+        <v>1.488923376</v>
       </c>
       <c r="N35">
-        <v>8.344868487999999</v>
+        <v>8.301076623999998</v>
       </c>
       <c r="O35">
-        <v>1.8775954098</v>
+        <v>1.8677422404</v>
       </c>
       <c r="P35">
-        <v>6.4672730782</v>
+        <v>6.433334383599998</v>
       </c>
       <c r="Q35">
-        <v>7.8772730782</v>
+        <v>7.843334383599998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2474385725907039</v>
+        <v>0.249996202256377</v>
       </c>
       <c r="T35">
-        <v>1.405913364229855</v>
+        <v>1.423746290150331</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.77446994872533</v>
+        <v>6.57522083258635</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1793055434892088</v>
+        <v>0.178940018342646</v>
       </c>
       <c r="C36">
-        <v>58.67324804294051</v>
+        <v>58.03916270269657</v>
       </c>
       <c r="D36">
-        <v>62.79356804294052</v>
+        <v>62.96596270269657</v>
       </c>
       <c r="E36">
-        <v>26.57232</v>
+        <v>27.3788</v>
       </c>
       <c r="F36">
-        <v>27.42032</v>
+        <v>28.2268</v>
       </c>
       <c r="G36">
         <v>23.3</v>
@@ -4239,28 +4239,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M36">
-        <v>1.488923376</v>
+        <v>1.53271524</v>
       </c>
       <c r="N36">
-        <v>8.301076623999998</v>
+        <v>8.257284759999999</v>
       </c>
       <c r="O36">
-        <v>1.8677422404</v>
+        <v>1.857889071</v>
       </c>
       <c r="P36">
-        <v>6.433334383599998</v>
+        <v>6.399395688999999</v>
       </c>
       <c r="Q36">
-        <v>7.843334383599998</v>
+        <v>7.809395689</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.249996202256377</v>
+        <v>0.2526325282194554</v>
       </c>
       <c r="T36">
-        <v>1.423746290150331</v>
+        <v>1.442127921483745</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.57522083258635</v>
+        <v>6.38735738022674</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.178940018342646</v>
+        <v>0.1785744931960832</v>
       </c>
       <c r="C37">
-        <v>58.03916270269657</v>
+        <v>57.40602655957261</v>
       </c>
       <c r="D37">
-        <v>62.96596270269657</v>
+        <v>63.13930655957262</v>
       </c>
       <c r="E37">
-        <v>27.3788</v>
+        <v>28.18528</v>
       </c>
       <c r="F37">
-        <v>28.2268</v>
+        <v>29.03328</v>
       </c>
       <c r="G37">
         <v>23.3</v>
@@ -4321,28 +4321,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M37">
-        <v>1.53271524</v>
+        <v>1.576507104</v>
       </c>
       <c r="N37">
-        <v>8.257284759999999</v>
+        <v>8.213492895999998</v>
       </c>
       <c r="O37">
-        <v>1.857889071</v>
+        <v>1.8480359016</v>
       </c>
       <c r="P37">
-        <v>6.399395688999999</v>
+        <v>6.365456994399999</v>
       </c>
       <c r="Q37">
-        <v>7.809395689</v>
+        <v>7.775456994399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2526325282194554</v>
+        <v>0.25535123936888</v>
       </c>
       <c r="T37">
-        <v>1.442127921483745</v>
+        <v>1.461083978796328</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.38735738022674</v>
+        <v>6.209930786331552</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1785744931960832</v>
+        <v>0.1784957180495205</v>
       </c>
       <c r="C38">
-        <v>57.4060265595726</v>
+        <v>56.63702936761803</v>
       </c>
       <c r="D38">
-        <v>63.1393065595726</v>
+        <v>63.17678936761803</v>
       </c>
       <c r="E38">
-        <v>28.18528</v>
+        <v>28.99176</v>
       </c>
       <c r="F38">
-        <v>29.03328</v>
+        <v>29.83976</v>
       </c>
       <c r="G38">
         <v>23.3</v>
@@ -4403,45 +4403,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M38">
-        <v>1.576507104</v>
+        <v>1.650138728</v>
       </c>
       <c r="N38">
-        <v>8.213492896</v>
+        <v>8.139861271999999</v>
       </c>
       <c r="O38">
-        <v>1.8480359016</v>
+        <v>1.8314687862</v>
       </c>
       <c r="P38">
-        <v>6.3654569944</v>
+        <v>6.308392485799999</v>
       </c>
       <c r="Q38">
-        <v>7.7754569944</v>
+        <v>7.718392485799999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.25535123936888</v>
+        <v>0.2581562588087627</v>
       </c>
       <c r="T38">
-        <v>1.461083978796328</v>
+        <v>1.480641815706137</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.225</v>
       </c>
       <c r="W38">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.209930786331554</v>
+        <v>5.932834514989942</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1784957180495205</v>
+        <v>0.1781379429029577</v>
       </c>
       <c r="C39">
-        <v>56.63702936761803</v>
+        <v>56.00134758753551</v>
       </c>
       <c r="D39">
-        <v>63.17678936761803</v>
+        <v>63.34758758753551</v>
       </c>
       <c r="E39">
-        <v>28.99176</v>
+        <v>29.79824</v>
       </c>
       <c r="F39">
-        <v>29.83976</v>
+        <v>30.64624</v>
       </c>
       <c r="G39">
         <v>23.3</v>
@@ -4485,28 +4485,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M39">
-        <v>1.650138728</v>
+        <v>1.694737072</v>
       </c>
       <c r="N39">
-        <v>8.139861271999999</v>
+        <v>8.095262927999999</v>
       </c>
       <c r="O39">
-        <v>1.8314687862</v>
+        <v>1.8214341588</v>
       </c>
       <c r="P39">
-        <v>6.308392485799999</v>
+        <v>6.273828769199999</v>
       </c>
       <c r="Q39">
-        <v>7.718392485799999</v>
+        <v>7.683828769199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2581562588087627</v>
+        <v>0.261051762746706</v>
       </c>
       <c r="T39">
-        <v>1.480641815706137</v>
+        <v>1.500830550580777</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.932834514989942</v>
+        <v>5.776707290911259</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1781379429029577</v>
+        <v>0.1777801677563949</v>
       </c>
       <c r="C40">
-        <v>56.00134758753551</v>
+        <v>55.36659181564349</v>
       </c>
       <c r="D40">
-        <v>63.34758758753551</v>
+        <v>63.51931181564349</v>
       </c>
       <c r="E40">
-        <v>29.79824</v>
+        <v>30.60472</v>
       </c>
       <c r="F40">
-        <v>30.64624</v>
+        <v>31.45272</v>
       </c>
       <c r="G40">
         <v>23.3</v>
@@ -4567,28 +4567,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M40">
-        <v>1.694737072</v>
+        <v>1.739335416</v>
       </c>
       <c r="N40">
-        <v>8.095262927999999</v>
+        <v>8.050664584</v>
       </c>
       <c r="O40">
-        <v>1.8214341588</v>
+        <v>1.8113995314</v>
       </c>
       <c r="P40">
-        <v>6.273828769199999</v>
+        <v>6.2392650526</v>
       </c>
       <c r="Q40">
-        <v>7.683828769199999</v>
+        <v>7.6492650526</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.261051762746706</v>
+        <v>0.2640422012399917</v>
       </c>
       <c r="T40">
-        <v>1.500830550580777</v>
+        <v>1.521681211189012</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.776707290911259</v>
+        <v>5.628586591144304</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1777801677563949</v>
+        <v>0.1774223926098321</v>
       </c>
       <c r="C41">
-        <v>55.36659181564349</v>
+        <v>54.73276960315064</v>
       </c>
       <c r="D41">
-        <v>63.51931181564349</v>
+        <v>63.69196960315063</v>
       </c>
       <c r="E41">
-        <v>30.60472</v>
+        <v>31.4112</v>
       </c>
       <c r="F41">
-        <v>31.45272</v>
+        <v>32.2592</v>
       </c>
       <c r="G41">
         <v>23.3</v>
@@ -4649,28 +4649,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M41">
-        <v>1.739335416</v>
+        <v>1.78393376</v>
       </c>
       <c r="N41">
-        <v>8.050664584</v>
+        <v>8.006066239999999</v>
       </c>
       <c r="O41">
-        <v>1.8113995314</v>
+        <v>1.801364904</v>
       </c>
       <c r="P41">
-        <v>6.2392650526</v>
+        <v>6.204701335999999</v>
       </c>
       <c r="Q41">
-        <v>7.6492650526</v>
+        <v>7.614701336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2640422012399917</v>
+        <v>0.2671323210163869</v>
       </c>
       <c r="T41">
-        <v>1.521681211189012</v>
+        <v>1.543226893817522</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.628586591144304</v>
+        <v>5.487871926365695</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1774223926098321</v>
+        <v>0.1770646174632694</v>
       </c>
       <c r="C42">
-        <v>54.73276960315064</v>
+        <v>54.09988858359189</v>
       </c>
       <c r="D42">
-        <v>63.69196960315063</v>
+        <v>63.86556858359189</v>
       </c>
       <c r="E42">
-        <v>31.4112</v>
+        <v>32.21768</v>
       </c>
       <c r="F42">
-        <v>32.2592</v>
+        <v>33.06568</v>
       </c>
       <c r="G42">
         <v>23.3</v>
@@ -4731,28 +4731,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M42">
-        <v>1.78393376</v>
+        <v>1.828532104</v>
       </c>
       <c r="N42">
-        <v>8.006066239999999</v>
+        <v>7.961467895999999</v>
       </c>
       <c r="O42">
-        <v>1.801364904</v>
+        <v>1.7913302766</v>
       </c>
       <c r="P42">
-        <v>6.204701335999999</v>
+        <v>6.170137619399999</v>
       </c>
       <c r="Q42">
-        <v>7.614701336</v>
+        <v>7.580137619399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2671323210163869</v>
+        <v>0.2703271906157109</v>
       </c>
       <c r="T42">
-        <v>1.543226893817522</v>
+        <v>1.565502938569032</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.487871926365695</v>
+        <v>5.354021391576289</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1770646174632694</v>
+        <v>0.1767068423167066</v>
       </c>
       <c r="C43">
-        <v>54.09988858359189</v>
+        <v>53.46795647395373</v>
       </c>
       <c r="D43">
-        <v>63.86556858359189</v>
+        <v>64.04011647395373</v>
       </c>
       <c r="E43">
-        <v>32.21768</v>
+        <v>33.02416</v>
       </c>
       <c r="F43">
-        <v>33.06568</v>
+        <v>33.87216</v>
       </c>
       <c r="G43">
         <v>23.3</v>
@@ -4813,28 +4813,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M43">
-        <v>1.828532104</v>
+        <v>1.873130448</v>
       </c>
       <c r="N43">
-        <v>7.961467895999999</v>
+        <v>7.916869551999999</v>
       </c>
       <c r="O43">
-        <v>1.7913302766</v>
+        <v>1.7812956492</v>
       </c>
       <c r="P43">
-        <v>6.170137619399999</v>
+        <v>6.135573902799999</v>
       </c>
       <c r="Q43">
-        <v>7.580137619399999</v>
+        <v>7.545573902799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2703271906157109</v>
+        <v>0.2736322281322528</v>
       </c>
       <c r="T43">
-        <v>1.565502938569032</v>
+        <v>1.588547122794732</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.354021391576289</v>
+        <v>5.226544691776852</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1767068423167066</v>
+        <v>0.1763490671701439</v>
       </c>
       <c r="C44">
-        <v>53.46795647395373</v>
+        <v>52.83698107581736</v>
       </c>
       <c r="D44">
-        <v>64.04011647395373</v>
+        <v>64.21562107581735</v>
       </c>
       <c r="E44">
-        <v>33.02415999999999</v>
+        <v>33.83064</v>
       </c>
       <c r="F44">
-        <v>33.87215999999999</v>
+        <v>34.67863999999999</v>
       </c>
       <c r="G44">
         <v>23.3</v>
@@ -4895,28 +4895,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M44">
-        <v>1.873130448</v>
+        <v>1.917728792</v>
       </c>
       <c r="N44">
-        <v>7.916869552</v>
+        <v>7.872271207999999</v>
       </c>
       <c r="O44">
-        <v>1.7812956492</v>
+        <v>1.7712610218</v>
       </c>
       <c r="P44">
-        <v>6.135573902799999</v>
+        <v>6.101010186199999</v>
       </c>
       <c r="Q44">
-        <v>7.545573902799999</v>
+        <v>7.511010186199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2736322281322527</v>
+        <v>0.2770532318774453</v>
       </c>
       <c r="T44">
-        <v>1.588547122794732</v>
+        <v>1.612399874888001</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.226544691776854</v>
+        <v>5.104997140805299</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1763490671701439</v>
+        <v>0.1759912920235811</v>
       </c>
       <c r="C45">
-        <v>52.83698107581736</v>
+        <v>52.20697027652134</v>
       </c>
       <c r="D45">
-        <v>64.21562107581735</v>
+        <v>64.39209027652134</v>
       </c>
       <c r="E45">
-        <v>33.83064</v>
+        <v>34.63712</v>
       </c>
       <c r="F45">
-        <v>34.67863999999999</v>
+        <v>35.48512</v>
       </c>
       <c r="G45">
         <v>23.3</v>
@@ -4977,28 +4977,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M45">
-        <v>1.917728792</v>
+        <v>1.962327136</v>
       </c>
       <c r="N45">
-        <v>7.872271207999999</v>
+        <v>7.827672863999999</v>
       </c>
       <c r="O45">
-        <v>1.7712610218</v>
+        <v>1.7612263944</v>
       </c>
       <c r="P45">
-        <v>6.101010186199999</v>
+        <v>6.066446469599999</v>
       </c>
       <c r="Q45">
-        <v>7.511010186199999</v>
+        <v>7.476446469599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2770532318774453</v>
+        <v>0.2805964143278233</v>
       </c>
       <c r="T45">
-        <v>1.612399874888001</v>
+        <v>1.637104510984601</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.104997140805299</v>
+        <v>4.988974478514269</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1759912920235811</v>
+        <v>0.1756335168770183</v>
       </c>
       <c r="C46">
-        <v>52.20697027652134</v>
+        <v>51.57793205034302</v>
       </c>
       <c r="D46">
-        <v>64.39209027652134</v>
+        <v>64.56953205034303</v>
       </c>
       <c r="E46">
-        <v>34.63712</v>
+        <v>35.4436</v>
       </c>
       <c r="F46">
-        <v>35.48512</v>
+        <v>36.2916</v>
       </c>
       <c r="G46">
         <v>23.3</v>
@@ -5059,28 +5059,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M46">
-        <v>1.962327136</v>
+        <v>2.00692548</v>
       </c>
       <c r="N46">
-        <v>7.827672863999999</v>
+        <v>7.78307452</v>
       </c>
       <c r="O46">
-        <v>1.7612263944</v>
+        <v>1.751191767</v>
       </c>
       <c r="P46">
-        <v>6.066446469599999</v>
+        <v>6.031882753</v>
       </c>
       <c r="Q46">
-        <v>7.476446469599999</v>
+        <v>7.441882753</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2805964143278233</v>
+        <v>0.2842684397763969</v>
       </c>
       <c r="T46">
-        <v>1.637104510984601</v>
+        <v>1.662707497484713</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.988974478514269</v>
+        <v>4.87810837899173</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1756335168770183</v>
+        <v>0.1752757417304555</v>
       </c>
       <c r="C47">
-        <v>51.57793205034302</v>
+        <v>50.94987445969978</v>
       </c>
       <c r="D47">
-        <v>64.56953205034303</v>
+        <v>64.74795445969978</v>
       </c>
       <c r="E47">
-        <v>35.4436</v>
+        <v>36.25008</v>
       </c>
       <c r="F47">
-        <v>36.2916</v>
+        <v>37.09808</v>
       </c>
       <c r="G47">
         <v>23.3</v>
@@ -5141,28 +5141,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M47">
-        <v>2.00692548</v>
+        <v>2.051523824</v>
       </c>
       <c r="N47">
-        <v>7.78307452</v>
+        <v>7.738476175999999</v>
       </c>
       <c r="O47">
-        <v>1.751191767</v>
+        <v>1.7411571396</v>
       </c>
       <c r="P47">
-        <v>6.031882753</v>
+        <v>5.997319036399999</v>
       </c>
       <c r="Q47">
-        <v>7.441882753</v>
+        <v>7.407319036399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2842684397763969</v>
+        <v>0.2880764661675102</v>
       </c>
       <c r="T47">
-        <v>1.662707497484713</v>
+        <v>1.689258742744088</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.87810837899173</v>
+        <v>4.772062544665822</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1752757417304555</v>
+        <v>0.1749179665838928</v>
       </c>
       <c r="C48">
-        <v>50.94987445969978</v>
+        <v>50.32280565637012</v>
       </c>
       <c r="D48">
-        <v>64.74795445969978</v>
+        <v>64.92736565637013</v>
       </c>
       <c r="E48">
-        <v>36.25008</v>
+        <v>37.05656</v>
       </c>
       <c r="F48">
-        <v>37.09808</v>
+        <v>37.90456</v>
       </c>
       <c r="G48">
         <v>23.3</v>
@@ -5223,28 +5223,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M48">
-        <v>2.051523824</v>
+        <v>2.096122168</v>
       </c>
       <c r="N48">
-        <v>7.738476175999999</v>
+        <v>7.693877831999998</v>
       </c>
       <c r="O48">
-        <v>1.7411571396</v>
+        <v>1.7311225122</v>
       </c>
       <c r="P48">
-        <v>5.997319036399999</v>
+        <v>5.962755319799999</v>
       </c>
       <c r="Q48">
-        <v>7.407319036399999</v>
+        <v>7.372755319799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2880764661675102</v>
+        <v>0.2920281916677222</v>
       </c>
       <c r="T48">
-        <v>1.689258742744088</v>
+        <v>1.716811921786837</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.772062544665822</v>
+        <v>4.670529299034634</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1749179665838928</v>
+        <v>0.17456019143733</v>
       </c>
       <c r="C49">
-        <v>50.32280565637012</v>
+        <v>49.69673388273524</v>
       </c>
       <c r="D49">
-        <v>64.92736565637013</v>
+        <v>65.10777388273524</v>
       </c>
       <c r="E49">
-        <v>37.05656</v>
+        <v>37.86304000000001</v>
       </c>
       <c r="F49">
-        <v>37.90456</v>
+        <v>38.71104</v>
       </c>
       <c r="G49">
         <v>23.3</v>
@@ -5305,28 +5305,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M49">
-        <v>2.096122168</v>
+        <v>2.140720512</v>
       </c>
       <c r="N49">
-        <v>7.693877831999998</v>
+        <v>7.649279487999999</v>
       </c>
       <c r="O49">
-        <v>1.7311225122</v>
+        <v>1.7210878848</v>
       </c>
       <c r="P49">
-        <v>5.962755319799999</v>
+        <v>5.928191603199999</v>
       </c>
       <c r="Q49">
-        <v>7.372755319799999</v>
+        <v>7.338191603199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2920281916677222</v>
+        <v>0.29613190661025</v>
       </c>
       <c r="T49">
-        <v>1.716811921786837</v>
+        <v>1.745424838485076</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.670529299034634</v>
+        <v>4.573226605304747</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.17456019143733</v>
+        <v>0.1751517912907672</v>
       </c>
       <c r="C50">
-        <v>49.69673388273524</v>
+        <v>48.59247872939341</v>
       </c>
       <c r="D50">
-        <v>65.10777388273524</v>
+        <v>64.80999872939341</v>
       </c>
       <c r="E50">
-        <v>37.86304</v>
+        <v>38.66952</v>
       </c>
       <c r="F50">
-        <v>38.71104</v>
+        <v>39.51752</v>
       </c>
       <c r="G50">
         <v>23.3</v>
@@ -5387,45 +5387,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M50">
-        <v>2.140720512</v>
+        <v>2.284112656</v>
       </c>
       <c r="N50">
-        <v>7.649279487999999</v>
+        <v>7.505887344</v>
       </c>
       <c r="O50">
-        <v>1.7210878848</v>
+        <v>1.6888246524</v>
       </c>
       <c r="P50">
-        <v>5.928191603199999</v>
+        <v>5.817062691599999</v>
       </c>
       <c r="Q50">
-        <v>7.338191603199999</v>
+        <v>7.2270626916</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.29613190661025</v>
+        <v>0.300396551550524</v>
       </c>
       <c r="T50">
-        <v>1.745424838485076</v>
+        <v>1.775159830347951</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.225</v>
       </c>
       <c r="W50">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.573226605304747</v>
+        <v>4.286128345851607</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1751517912907672</v>
+        <v>0.1748133911442044</v>
       </c>
       <c r="C51">
-        <v>48.59247872939341</v>
+        <v>47.95599436220526</v>
       </c>
       <c r="D51">
-        <v>64.80999872939341</v>
+        <v>64.97999436220526</v>
       </c>
       <c r="E51">
-        <v>38.66952</v>
+        <v>39.476</v>
       </c>
       <c r="F51">
-        <v>39.51752</v>
+        <v>40.324</v>
       </c>
       <c r="G51">
         <v>23.3</v>
@@ -5469,28 +5469,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M51">
-        <v>2.284112656</v>
+        <v>2.3307272</v>
       </c>
       <c r="N51">
-        <v>7.505887344</v>
+        <v>7.459272799999999</v>
       </c>
       <c r="O51">
-        <v>1.6888246524</v>
+        <v>1.67833638</v>
       </c>
       <c r="P51">
-        <v>5.817062691599999</v>
+        <v>5.78093642</v>
       </c>
       <c r="Q51">
-        <v>7.2270626916</v>
+        <v>7.19093642</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.300396551550524</v>
+        <v>0.3048317822884088</v>
       </c>
       <c r="T51">
-        <v>1.775159830347951</v>
+        <v>1.806084221885341</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.286128345851607</v>
+        <v>4.200405778934574</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1748133911442044</v>
+        <v>0.1744749909976417</v>
       </c>
       <c r="C52">
-        <v>47.95599436220526</v>
+        <v>47.32040413220121</v>
       </c>
       <c r="D52">
-        <v>64.97999436220526</v>
+        <v>65.15088413220121</v>
       </c>
       <c r="E52">
-        <v>39.476</v>
+        <v>40.28248</v>
       </c>
       <c r="F52">
-        <v>40.324</v>
+        <v>41.13048</v>
       </c>
       <c r="G52">
         <v>23.3</v>
@@ -5551,28 +5551,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M52">
-        <v>2.3307272</v>
+        <v>2.377341744</v>
       </c>
       <c r="N52">
-        <v>7.459272799999999</v>
+        <v>7.412658255999999</v>
       </c>
       <c r="O52">
-        <v>1.67833638</v>
+        <v>1.6678481076</v>
       </c>
       <c r="P52">
-        <v>5.78093642</v>
+        <v>5.744810148399999</v>
       </c>
       <c r="Q52">
-        <v>7.19093642</v>
+        <v>7.154810148399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3048317822884088</v>
+        <v>0.30944804285233</v>
       </c>
       <c r="T52">
-        <v>1.806084221885341</v>
+        <v>1.838270833485483</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.200405778934574</v>
+        <v>4.118044881308405</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1744749909976417</v>
+        <v>0.1741365908510789</v>
       </c>
       <c r="C53">
-        <v>47.32040413220121</v>
+        <v>46.68571511241053</v>
       </c>
       <c r="D53">
-        <v>65.15088413220121</v>
+        <v>65.32267511241054</v>
       </c>
       <c r="E53">
-        <v>40.28248</v>
+        <v>41.08896</v>
       </c>
       <c r="F53">
-        <v>41.13048</v>
+        <v>41.93696</v>
       </c>
       <c r="G53">
         <v>23.3</v>
@@ -5633,28 +5633,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M53">
-        <v>2.377341744</v>
+        <v>2.423956288</v>
       </c>
       <c r="N53">
-        <v>7.412658255999999</v>
+        <v>7.366043711999999</v>
       </c>
       <c r="O53">
-        <v>1.6678481076</v>
+        <v>1.6573598352</v>
       </c>
       <c r="P53">
-        <v>5.744810148399999</v>
+        <v>5.708683876799999</v>
       </c>
       <c r="Q53">
-        <v>7.154810148399999</v>
+        <v>7.118683876799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.30944804285233</v>
+        <v>0.3142566476064144</v>
       </c>
       <c r="T53">
-        <v>1.838270833485483</v>
+        <v>1.871798553902297</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.118044881308405</v>
+        <v>4.038851710514013</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1741365908510789</v>
+        <v>0.1752358157045161</v>
       </c>
       <c r="C54">
-        <v>46.68571511241053</v>
+        <v>45.32448674090502</v>
       </c>
       <c r="D54">
-        <v>65.32267511241054</v>
+        <v>64.76792674090503</v>
       </c>
       <c r="E54">
-        <v>41.08896</v>
+        <v>41.89544</v>
       </c>
       <c r="F54">
-        <v>41.93696</v>
+        <v>42.74344</v>
       </c>
       <c r="G54">
         <v>23.3</v>
@@ -5715,45 +5715,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M54">
-        <v>2.423956288</v>
+        <v>2.620172872</v>
       </c>
       <c r="N54">
-        <v>7.366043711999999</v>
+        <v>7.169827128</v>
       </c>
       <c r="O54">
-        <v>1.6573598352</v>
+        <v>1.6132111038</v>
       </c>
       <c r="P54">
-        <v>5.708683876799999</v>
+        <v>5.5566160242</v>
       </c>
       <c r="Q54">
-        <v>7.118683876799999</v>
+        <v>6.9666160242</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3142566476064144</v>
+        <v>0.319269873839396</v>
       </c>
       <c r="T54">
-        <v>1.871798553902297</v>
+        <v>1.906752985826209</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.225</v>
       </c>
       <c r="W54">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.038851710514013</v>
+        <v>3.736394687777685</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1752358157045161</v>
+        <v>0.1749245405579534</v>
       </c>
       <c r="C55">
-        <v>45.32448674090502</v>
+        <v>44.67414008164509</v>
       </c>
       <c r="D55">
-        <v>64.76792674090503</v>
+        <v>64.9240600816451</v>
       </c>
       <c r="E55">
-        <v>41.89544</v>
+        <v>42.70192</v>
       </c>
       <c r="F55">
-        <v>42.74344</v>
+        <v>43.54992</v>
       </c>
       <c r="G55">
         <v>23.3</v>
@@ -5797,28 +5797,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M55">
-        <v>2.620172872</v>
+        <v>2.669610096</v>
       </c>
       <c r="N55">
-        <v>7.169827128</v>
+        <v>7.120389904</v>
       </c>
       <c r="O55">
-        <v>1.6132111038</v>
+        <v>1.6020877284</v>
       </c>
       <c r="P55">
-        <v>5.5566160242</v>
+        <v>5.5183021756</v>
       </c>
       <c r="Q55">
-        <v>6.9666160242</v>
+        <v>6.9283021756</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.319269873839396</v>
+        <v>0.3245010664303334</v>
       </c>
       <c r="T55">
-        <v>1.906752985826209</v>
+        <v>1.943227175659856</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.736394687777685</v>
+        <v>3.66720219355958</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1749245405579534</v>
+        <v>0.1746132654113906</v>
       </c>
       <c r="C56">
-        <v>44.67414008164509</v>
+        <v>44.02454800970767</v>
       </c>
       <c r="D56">
-        <v>64.9240600816451</v>
+        <v>65.08094800970767</v>
       </c>
       <c r="E56">
-        <v>42.70192</v>
+        <v>43.5084</v>
       </c>
       <c r="F56">
-        <v>43.54992</v>
+        <v>44.3564</v>
       </c>
       <c r="G56">
         <v>23.3</v>
@@ -5879,28 +5879,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M56">
-        <v>2.669610096</v>
+        <v>2.71904732</v>
       </c>
       <c r="N56">
-        <v>7.120389904</v>
+        <v>7.07095268</v>
       </c>
       <c r="O56">
-        <v>1.6020877284</v>
+        <v>1.590964353</v>
       </c>
       <c r="P56">
-        <v>5.5183021756</v>
+        <v>5.479988326999999</v>
       </c>
       <c r="Q56">
-        <v>6.9283021756</v>
+        <v>6.889988326999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3245010664303334</v>
+        <v>0.3299647564697569</v>
       </c>
       <c r="T56">
-        <v>1.943227175659856</v>
+        <v>1.981322440597222</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.66720219355958</v>
+        <v>3.600525790040314</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1746132654113906</v>
+        <v>0.1743019902648278</v>
       </c>
       <c r="C57">
-        <v>44.02454800970767</v>
+        <v>43.37571600868742</v>
       </c>
       <c r="D57">
-        <v>65.08094800970767</v>
+        <v>65.23859600868742</v>
       </c>
       <c r="E57">
-        <v>43.5084</v>
+        <v>44.31488</v>
       </c>
       <c r="F57">
-        <v>44.3564</v>
+        <v>45.16288</v>
       </c>
       <c r="G57">
         <v>23.3</v>
@@ -5961,28 +5961,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M57">
-        <v>2.71904732</v>
+        <v>2.768484544</v>
       </c>
       <c r="N57">
-        <v>7.07095268</v>
+        <v>7.021515455999999</v>
       </c>
       <c r="O57">
-        <v>1.590964353</v>
+        <v>1.5798409776</v>
       </c>
       <c r="P57">
-        <v>5.479988326999999</v>
+        <v>5.4416744784</v>
       </c>
       <c r="Q57">
-        <v>6.889988326999999</v>
+        <v>6.8516744784</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3299647564697569</v>
+        <v>0.3356767960564269</v>
       </c>
       <c r="T57">
-        <v>1.981322440597222</v>
+        <v>2.021149308486285</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.600525790040314</v>
+        <v>3.536230686646737</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1743019902648278</v>
+        <v>0.175227615118265</v>
       </c>
       <c r="C58">
-        <v>43.37571600868742</v>
+        <v>42.10267046304391</v>
       </c>
       <c r="D58">
-        <v>65.23859600868742</v>
+        <v>64.77203046304392</v>
       </c>
       <c r="E58">
-        <v>44.31488</v>
+        <v>45.12136</v>
       </c>
       <c r="F58">
-        <v>45.16288</v>
+        <v>45.96936</v>
       </c>
       <c r="G58">
         <v>23.3</v>
@@ -6043,45 +6043,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M58">
-        <v>2.768484544</v>
+        <v>2.946635976</v>
       </c>
       <c r="N58">
-        <v>7.021515455999999</v>
+        <v>6.843364023999999</v>
       </c>
       <c r="O58">
-        <v>1.5798409776</v>
+        <v>1.5397569054</v>
       </c>
       <c r="P58">
-        <v>5.4416744784</v>
+        <v>5.303607118599999</v>
       </c>
       <c r="Q58">
-        <v>6.8516744784</v>
+        <v>6.713607118599999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3356767960564269</v>
+        <v>0.3416545119029419</v>
       </c>
       <c r="T58">
-        <v>2.021149308486285</v>
+        <v>2.062828588835305</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.225</v>
       </c>
       <c r="W58">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.536230686646737</v>
+        <v>3.322432794460661</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.175227615118265</v>
+        <v>0.1749380399717023</v>
       </c>
       <c r="C59">
-        <v>42.10267046304391</v>
+        <v>41.44143326074018</v>
       </c>
       <c r="D59">
-        <v>64.77203046304392</v>
+        <v>64.91727326074019</v>
       </c>
       <c r="E59">
-        <v>45.12136</v>
+        <v>45.92784</v>
       </c>
       <c r="F59">
-        <v>45.96936</v>
+        <v>46.77584</v>
       </c>
       <c r="G59">
         <v>23.3</v>
@@ -6125,28 +6125,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M59">
-        <v>2.946635976</v>
+        <v>2.998331344</v>
       </c>
       <c r="N59">
-        <v>6.843364023999999</v>
+        <v>6.791668655999999</v>
       </c>
       <c r="O59">
-        <v>1.5397569054</v>
+        <v>1.5281254476</v>
       </c>
       <c r="P59">
-        <v>5.303607118599999</v>
+        <v>5.263543208399999</v>
       </c>
       <c r="Q59">
-        <v>6.713607118599999</v>
+        <v>6.673543208399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3416545119029419</v>
+        <v>0.3479168808850054</v>
       </c>
       <c r="T59">
-        <v>2.062828588835305</v>
+        <v>2.106492596819993</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.322432794460661</v>
+        <v>3.265149470418236</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1749380399717023</v>
+        <v>0.1746484648251395</v>
       </c>
       <c r="C60">
-        <v>41.44143326074019</v>
+        <v>40.78084889825861</v>
       </c>
       <c r="D60">
-        <v>64.91727326074019</v>
+        <v>65.06316889825861</v>
       </c>
       <c r="E60">
-        <v>45.92784</v>
+        <v>46.73432</v>
       </c>
       <c r="F60">
-        <v>46.77584</v>
+        <v>47.58232</v>
       </c>
       <c r="G60">
         <v>23.3</v>
@@ -6207,28 +6207,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M60">
-        <v>2.998331344</v>
+        <v>3.050026712</v>
       </c>
       <c r="N60">
-        <v>6.791668655999999</v>
+        <v>6.739973288</v>
       </c>
       <c r="O60">
-        <v>1.5281254476</v>
+        <v>1.5164939898</v>
       </c>
       <c r="P60">
-        <v>5.263543208399999</v>
+        <v>5.2234792982</v>
       </c>
       <c r="Q60">
-        <v>6.673543208399999</v>
+        <v>6.6334792982</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3479168808850053</v>
+        <v>0.354484731280828</v>
       </c>
       <c r="T60">
-        <v>2.106492596819992</v>
+        <v>2.152286556413689</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.265149470418236</v>
+        <v>3.20980795397047</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1746484648251395</v>
+        <v>0.1743588896785767</v>
       </c>
       <c r="C61">
-        <v>40.78084889825861</v>
+        <v>40.12092178710713</v>
       </c>
       <c r="D61">
-        <v>65.06316889825861</v>
+        <v>65.20972178710713</v>
       </c>
       <c r="E61">
-        <v>46.73432</v>
+        <v>47.5408</v>
       </c>
       <c r="F61">
-        <v>47.58232</v>
+        <v>48.3888</v>
       </c>
       <c r="G61">
         <v>23.3</v>
@@ -6289,28 +6289,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M61">
-        <v>3.050026712</v>
+        <v>3.10172208</v>
       </c>
       <c r="N61">
-        <v>6.739973288</v>
+        <v>6.688277919999999</v>
       </c>
       <c r="O61">
-        <v>1.5164939898</v>
+        <v>1.504862532</v>
       </c>
       <c r="P61">
-        <v>5.2234792982</v>
+        <v>5.183415387999999</v>
       </c>
       <c r="Q61">
-        <v>6.6334792982</v>
+        <v>6.593415387999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.354484731280828</v>
+        <v>0.3613809741964418</v>
       </c>
       <c r="T61">
-        <v>2.152286556413689</v>
+        <v>2.200370213987071</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.20980795397047</v>
+        <v>3.156311154737629</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1743588896785767</v>
+        <v>0.174069314532014</v>
       </c>
       <c r="C62">
-        <v>40.12092178710713</v>
+        <v>39.46165637863054</v>
       </c>
       <c r="D62">
-        <v>65.20972178710713</v>
+        <v>65.35693637863054</v>
       </c>
       <c r="E62">
-        <v>47.5408</v>
+        <v>48.34728</v>
       </c>
       <c r="F62">
-        <v>48.3888</v>
+        <v>49.19528</v>
       </c>
       <c r="G62">
         <v>23.3</v>
@@ -6371,28 +6371,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M62">
-        <v>3.10172208</v>
+        <v>3.153417448</v>
       </c>
       <c r="N62">
-        <v>6.688277919999999</v>
+        <v>6.636582551999999</v>
       </c>
       <c r="O62">
-        <v>1.504862532</v>
+        <v>1.4932310742</v>
       </c>
       <c r="P62">
-        <v>5.183415387999999</v>
+        <v>5.1433514778</v>
       </c>
       <c r="Q62">
-        <v>6.593415387999999</v>
+        <v>6.5533514778</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3613809741964418</v>
+        <v>0.3686308705949076</v>
       </c>
       <c r="T62">
-        <v>2.200370213987071</v>
+        <v>2.25091970015396</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.156311154737629</v>
+        <v>3.104568348922258</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.174069314532014</v>
+        <v>0.1737797393854512</v>
       </c>
       <c r="C63">
-        <v>39.46165637863054</v>
+        <v>38.80305716446129</v>
       </c>
       <c r="D63">
-        <v>65.35693637863054</v>
+        <v>65.50481716446129</v>
       </c>
       <c r="E63">
-        <v>48.34728</v>
+        <v>49.15376</v>
       </c>
       <c r="F63">
-        <v>49.19528</v>
+        <v>50.00176</v>
       </c>
       <c r="G63">
         <v>23.3</v>
@@ -6453,28 +6453,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M63">
-        <v>3.153417448</v>
+        <v>3.205112816</v>
       </c>
       <c r="N63">
-        <v>6.636582551999999</v>
+        <v>6.584887183999999</v>
       </c>
       <c r="O63">
-        <v>1.4932310742</v>
+        <v>1.4815996164</v>
       </c>
       <c r="P63">
-        <v>5.1433514778</v>
+        <v>5.1032875676</v>
       </c>
       <c r="Q63">
-        <v>6.5533514778</v>
+        <v>6.5132875676</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3686308705949076</v>
+        <v>0.3762623404880294</v>
       </c>
       <c r="T63">
-        <v>2.25091970015396</v>
+        <v>2.304129685592789</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.104568348922258</v>
+        <v>3.054494665875124</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1737797393854512</v>
+        <v>0.1734901642388884</v>
       </c>
       <c r="C64">
-        <v>38.80305716446129</v>
+        <v>38.14512867697623</v>
       </c>
       <c r="D64">
-        <v>65.50481716446129</v>
+        <v>65.65336867697623</v>
       </c>
       <c r="E64">
-        <v>49.15376</v>
+        <v>49.96024</v>
       </c>
       <c r="F64">
-        <v>50.00176</v>
+        <v>50.80824</v>
       </c>
       <c r="G64">
         <v>23.3</v>
@@ -6535,28 +6535,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M64">
-        <v>3.205112816</v>
+        <v>3.256808184</v>
       </c>
       <c r="N64">
-        <v>6.584887183999999</v>
+        <v>6.533191815999999</v>
       </c>
       <c r="O64">
-        <v>1.4815996164</v>
+        <v>1.4699681586</v>
       </c>
       <c r="P64">
-        <v>5.1032875676</v>
+        <v>5.063223657399999</v>
       </c>
       <c r="Q64">
-        <v>6.5132875676</v>
+        <v>6.473223657399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3762623404880294</v>
+        <v>0.3843063222672659</v>
       </c>
       <c r="T64">
-        <v>2.304129685592789</v>
+        <v>2.360215886460745</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.054494665875124</v>
+        <v>3.006010623559646</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1734901642388884</v>
+        <v>0.1770693890923257</v>
       </c>
       <c r="C65">
-        <v>38.14512867697623</v>
+        <v>35.5485270766141</v>
       </c>
       <c r="D65">
-        <v>65.65336867697623</v>
+        <v>63.86324707661409</v>
       </c>
       <c r="E65">
-        <v>49.96024</v>
+        <v>50.76672</v>
       </c>
       <c r="F65">
-        <v>50.80824</v>
+        <v>51.61472</v>
       </c>
       <c r="G65">
         <v>23.3</v>
@@ -6617,45 +6617,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M65">
-        <v>3.256808184</v>
+        <v>3.711098368</v>
       </c>
       <c r="N65">
-        <v>6.533191815999999</v>
+        <v>6.078901631999999</v>
       </c>
       <c r="O65">
-        <v>1.4699681586</v>
+        <v>1.3677528672</v>
       </c>
       <c r="P65">
-        <v>5.063223657399999</v>
+        <v>4.711148764799999</v>
       </c>
       <c r="Q65">
-        <v>6.473223657399999</v>
+        <v>6.121148764799999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3843063222672659</v>
+        <v>0.3927971919231268</v>
       </c>
       <c r="T65">
-        <v>2.360215886460745</v>
+        <v>2.419417987376921</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.225</v>
       </c>
       <c r="W65">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.006010623559646</v>
+        <v>2.638033010500895</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1770693890923257</v>
+        <v>0.1768402639457629</v>
       </c>
       <c r="C66">
-        <v>35.5485270766141</v>
+        <v>34.85371257091181</v>
       </c>
       <c r="D66">
-        <v>63.86324707661409</v>
+        <v>63.97491257091181</v>
       </c>
       <c r="E66">
-        <v>50.76672</v>
+        <v>51.5732</v>
       </c>
       <c r="F66">
-        <v>51.61472</v>
+        <v>52.4212</v>
       </c>
       <c r="G66">
         <v>23.3</v>
@@ -6699,28 +6699,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M66">
-        <v>3.711098368</v>
+        <v>3.76908428</v>
       </c>
       <c r="N66">
-        <v>6.078901631999999</v>
+        <v>6.020915719999999</v>
       </c>
       <c r="O66">
-        <v>1.3677528672</v>
+        <v>1.354706037</v>
       </c>
       <c r="P66">
-        <v>4.711148764799999</v>
+        <v>4.666209682999999</v>
       </c>
       <c r="Q66">
-        <v>6.121148764799999</v>
+        <v>6.076209682999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3927971919231268</v>
+        <v>0.401773254130751</v>
       </c>
       <c r="T66">
-        <v>2.419417987376921</v>
+        <v>2.482003065488307</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.638033010500895</v>
+        <v>2.59744788726242</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1768402639457629</v>
+        <v>0.1766111387992001</v>
       </c>
       <c r="C67">
-        <v>34.85371257091181</v>
+        <v>34.15928924554752</v>
       </c>
       <c r="D67">
-        <v>63.97491257091181</v>
+        <v>64.08696924554752</v>
       </c>
       <c r="E67">
-        <v>51.5732</v>
+        <v>52.37968</v>
       </c>
       <c r="F67">
-        <v>52.4212</v>
+        <v>53.22768</v>
       </c>
       <c r="G67">
         <v>23.3</v>
@@ -6781,28 +6781,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M67">
-        <v>3.76908428</v>
+        <v>3.827070192</v>
       </c>
       <c r="N67">
-        <v>6.020915719999999</v>
+        <v>5.962929807999998</v>
       </c>
       <c r="O67">
-        <v>1.354706037</v>
+        <v>1.3416592068</v>
       </c>
       <c r="P67">
-        <v>4.666209682999999</v>
+        <v>4.621270601199999</v>
       </c>
       <c r="Q67">
-        <v>6.076209682999999</v>
+        <v>6.031270601199999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.401773254130751</v>
+        <v>0.4112773199976474</v>
       </c>
       <c r="T67">
-        <v>2.482003065488307</v>
+        <v>2.548269618782715</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.59744788726242</v>
+        <v>2.558092616243292</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1766111387992001</v>
+        <v>0.1763820136526373</v>
       </c>
       <c r="C68">
-        <v>34.15928924554752</v>
+        <v>33.46525915966977</v>
       </c>
       <c r="D68">
-        <v>64.08696924554752</v>
+        <v>64.19941915966977</v>
       </c>
       <c r="E68">
-        <v>52.37968</v>
+        <v>53.18616</v>
       </c>
       <c r="F68">
-        <v>53.22768</v>
+        <v>54.03416</v>
       </c>
       <c r="G68">
         <v>23.3</v>
@@ -6863,28 +6863,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M68">
-        <v>3.827070192</v>
+        <v>3.885056104</v>
       </c>
       <c r="N68">
-        <v>5.962929807999998</v>
+        <v>5.904943895999999</v>
       </c>
       <c r="O68">
-        <v>1.3416592068</v>
+        <v>1.3286123766</v>
       </c>
       <c r="P68">
-        <v>4.621270601199999</v>
+        <v>4.576331519399999</v>
       </c>
       <c r="Q68">
-        <v>6.031270601199999</v>
+        <v>5.986331519399999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4112773199976474</v>
+        <v>0.4213573898564768</v>
       </c>
       <c r="T68">
-        <v>2.548269618782715</v>
+        <v>2.618552326822239</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.558092616243292</v>
+        <v>2.519912129433691</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1763820136526373</v>
+        <v>0.1782081885060745</v>
       </c>
       <c r="C69">
-        <v>33.46525915966977</v>
+        <v>31.7733402287589</v>
       </c>
       <c r="D69">
-        <v>64.19941915966977</v>
+        <v>63.31398022875891</v>
       </c>
       <c r="E69">
-        <v>53.18616</v>
+        <v>53.99264</v>
       </c>
       <c r="F69">
-        <v>54.03416</v>
+        <v>54.84064</v>
       </c>
       <c r="G69">
         <v>23.3</v>
@@ -6945,45 +6945,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M69">
-        <v>3.885056104</v>
+        <v>4.156920512</v>
       </c>
       <c r="N69">
-        <v>5.904943895999999</v>
+        <v>5.633079487999999</v>
       </c>
       <c r="O69">
-        <v>1.3286123766</v>
+        <v>1.2674428848</v>
       </c>
       <c r="P69">
-        <v>4.576331519399999</v>
+        <v>4.365636603199999</v>
       </c>
       <c r="Q69">
-        <v>5.986331519399999</v>
+        <v>5.775636603199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4213573898564768</v>
+        <v>0.432067464081483</v>
       </c>
       <c r="T69">
-        <v>2.618552326822239</v>
+        <v>2.693227704114233</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.225</v>
       </c>
       <c r="W69">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.519912129433691</v>
+        <v>2.355108781064899</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1782081885060745</v>
+        <v>0.1780092883595118</v>
       </c>
       <c r="C70">
-        <v>31.7733402287589</v>
+        <v>31.06211193235121</v>
       </c>
       <c r="D70">
-        <v>63.31398022875891</v>
+        <v>63.40923193235121</v>
       </c>
       <c r="E70">
-        <v>53.99264</v>
+        <v>54.79912</v>
       </c>
       <c r="F70">
-        <v>54.84064</v>
+        <v>55.64712</v>
       </c>
       <c r="G70">
         <v>23.3</v>
@@ -7027,28 +7027,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M70">
-        <v>4.156920512</v>
+        <v>4.218051696000001</v>
       </c>
       <c r="N70">
-        <v>5.633079487999999</v>
+        <v>5.571948303999998</v>
       </c>
       <c r="O70">
-        <v>1.2674428848</v>
+        <v>1.2536883684</v>
       </c>
       <c r="P70">
-        <v>4.365636603199999</v>
+        <v>4.318259935599999</v>
       </c>
       <c r="Q70">
-        <v>5.775636603199999</v>
+        <v>5.728259935599999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.432067464081483</v>
+        <v>0.4434685108371348</v>
       </c>
       <c r="T70">
-        <v>2.693227704114233</v>
+        <v>2.77272084768313</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.355108781064899</v>
+        <v>2.320976769745118</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1780092883595118</v>
+        <v>0.177810388212949</v>
       </c>
       <c r="C71">
-        <v>31.06211193235121</v>
+        <v>30.35117066756374</v>
       </c>
       <c r="D71">
-        <v>63.40923193235121</v>
+        <v>63.50477066756374</v>
       </c>
       <c r="E71">
-        <v>54.79912</v>
+        <v>55.6056</v>
       </c>
       <c r="F71">
-        <v>55.64712</v>
+        <v>56.4536</v>
       </c>
       <c r="G71">
         <v>23.3</v>
@@ -7109,28 +7109,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M71">
-        <v>4.218051696000001</v>
+        <v>4.27918288</v>
       </c>
       <c r="N71">
-        <v>5.571948303999998</v>
+        <v>5.510817119999999</v>
       </c>
       <c r="O71">
-        <v>1.2536883684</v>
+        <v>1.239933852</v>
       </c>
       <c r="P71">
-        <v>4.318259935599999</v>
+        <v>4.270883267999999</v>
       </c>
       <c r="Q71">
-        <v>5.728259935599999</v>
+        <v>5.680883267999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4434685108371348</v>
+        <v>0.4556296273764968</v>
       </c>
       <c r="T71">
-        <v>2.77272084768313</v>
+        <v>2.857513534156621</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.320976769745118</v>
+        <v>2.287819958748759</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.177810388212949</v>
+        <v>0.1776114880663862</v>
       </c>
       <c r="C72">
-        <v>30.35117066756374</v>
+        <v>29.64051773376644</v>
       </c>
       <c r="D72">
-        <v>63.50477066756374</v>
+        <v>63.60059773376644</v>
       </c>
       <c r="E72">
-        <v>55.6056</v>
+        <v>56.41208</v>
       </c>
       <c r="F72">
-        <v>56.4536</v>
+        <v>57.26008</v>
       </c>
       <c r="G72">
         <v>23.3</v>
@@ -7191,28 +7191,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M72">
-        <v>4.27918288</v>
+        <v>4.340314064</v>
       </c>
       <c r="N72">
-        <v>5.510817119999999</v>
+        <v>5.449685935999999</v>
       </c>
       <c r="O72">
-        <v>1.239933852</v>
+        <v>1.2261793356</v>
       </c>
       <c r="P72">
-        <v>4.270883267999999</v>
+        <v>4.223506600399999</v>
       </c>
       <c r="Q72">
-        <v>5.680883267999999</v>
+        <v>5.6335066004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4556296273764968</v>
+        <v>0.4686294416082284</v>
       </c>
       <c r="T72">
-        <v>2.857513534156621</v>
+        <v>2.948153992111041</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.287819958748759</v>
+        <v>2.255597142428355</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1776114880663862</v>
+        <v>0.1774125879198235</v>
       </c>
       <c r="C73">
-        <v>29.64051773376644</v>
+        <v>28.93015443818402</v>
       </c>
       <c r="D73">
-        <v>63.60059773376643</v>
+        <v>63.69671443818402</v>
       </c>
       <c r="E73">
-        <v>56.41208</v>
+        <v>57.21856</v>
       </c>
       <c r="F73">
-        <v>57.26007999999999</v>
+        <v>58.06656</v>
       </c>
       <c r="G73">
         <v>23.3</v>
@@ -7273,28 +7273,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M73">
-        <v>4.340314064</v>
+        <v>4.401445248</v>
       </c>
       <c r="N73">
-        <v>5.449685935999999</v>
+        <v>5.388554751999999</v>
       </c>
       <c r="O73">
-        <v>1.2261793356</v>
+        <v>1.2124248192</v>
       </c>
       <c r="P73">
-        <v>4.223506600399999</v>
+        <v>4.176129932799999</v>
       </c>
       <c r="Q73">
-        <v>5.6335066004</v>
+        <v>5.5861299328</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4686294416082283</v>
+        <v>0.4825578139993695</v>
       </c>
       <c r="T73">
-        <v>2.94815399211104</v>
+        <v>3.045268768490777</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.255597142428355</v>
+        <v>2.224269404339072</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1774125879198235</v>
+        <v>0.1772136877732607</v>
       </c>
       <c r="C74">
-        <v>28.93015443818402</v>
+        <v>28.22008209595544</v>
       </c>
       <c r="D74">
-        <v>63.69671443818402</v>
+        <v>63.79312209595544</v>
       </c>
       <c r="E74">
-        <v>57.21856</v>
+        <v>58.02504</v>
       </c>
       <c r="F74">
-        <v>58.06656</v>
+        <v>58.87304</v>
       </c>
       <c r="G74">
         <v>23.3</v>
@@ -7355,28 +7355,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M74">
-        <v>4.401445248</v>
+        <v>4.462576432</v>
       </c>
       <c r="N74">
-        <v>5.388554751999999</v>
+        <v>5.327423567999999</v>
       </c>
       <c r="O74">
-        <v>1.2124248192</v>
+        <v>1.1986703028</v>
       </c>
       <c r="P74">
-        <v>4.176129932799999</v>
+        <v>4.128753265199999</v>
       </c>
       <c r="Q74">
-        <v>5.5861299328</v>
+        <v>5.5387532652</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4825578139993695</v>
+        <v>0.4975179176787432</v>
       </c>
       <c r="T74">
-        <v>3.045268768490777</v>
+        <v>3.149577232009753</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.224269404339072</v>
+        <v>2.193799960444016</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1772136877732607</v>
+        <v>0.1770147876266979</v>
       </c>
       <c r="C75">
-        <v>28.22008209595544</v>
+        <v>27.51030203019366</v>
       </c>
       <c r="D75">
-        <v>63.79312209595544</v>
+        <v>63.88982203019365</v>
       </c>
       <c r="E75">
-        <v>58.02504</v>
+        <v>58.83152</v>
       </c>
       <c r="F75">
-        <v>58.87304</v>
+        <v>59.67952</v>
       </c>
       <c r="G75">
         <v>23.3</v>
@@ -7437,28 +7437,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M75">
-        <v>4.462576432</v>
+        <v>4.523707616</v>
       </c>
       <c r="N75">
-        <v>5.327423567999999</v>
+        <v>5.266292383999999</v>
       </c>
       <c r="O75">
-        <v>1.1986703028</v>
+        <v>1.1849157864</v>
       </c>
       <c r="P75">
-        <v>4.128753265199999</v>
+        <v>4.081376597599999</v>
       </c>
       <c r="Q75">
-        <v>5.5387532652</v>
+        <v>5.4913765976</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4975179176787432</v>
+        <v>0.5136287985642227</v>
       </c>
       <c r="T75">
-        <v>3.149577232009753</v>
+        <v>3.261909423491727</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.193799960444016</v>
+        <v>2.164154015032611</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1770147876266979</v>
+        <v>0.1768158874801352</v>
       </c>
       <c r="C76">
-        <v>27.51030203019366</v>
+        <v>26.80081557204635</v>
       </c>
       <c r="D76">
-        <v>63.88982203019365</v>
+        <v>63.98681557204635</v>
       </c>
       <c r="E76">
-        <v>58.83152</v>
+        <v>59.638</v>
       </c>
       <c r="F76">
-        <v>59.67952</v>
+        <v>60.486</v>
       </c>
       <c r="G76">
         <v>23.3</v>
@@ -7519,28 +7519,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M76">
-        <v>4.523707616</v>
+        <v>4.5848388</v>
       </c>
       <c r="N76">
-        <v>5.266292383999999</v>
+        <v>5.205161199999999</v>
       </c>
       <c r="O76">
-        <v>1.1849157864</v>
+        <v>1.17116127</v>
       </c>
       <c r="P76">
-        <v>4.081376597599999</v>
+        <v>4.033999929999999</v>
       </c>
       <c r="Q76">
-        <v>5.4913765976</v>
+        <v>5.443999929999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5136287985642227</v>
+        <v>0.5310285499205406</v>
       </c>
       <c r="T76">
-        <v>3.261909423491727</v>
+        <v>3.38322819029226</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.164154015032611</v>
+        <v>2.135298628165509</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1768158874801352</v>
+        <v>0.1766169873335724</v>
       </c>
       <c r="C77">
-        <v>26.80081557204635</v>
+        <v>26.09162406075703</v>
       </c>
       <c r="D77">
-        <v>63.98681557204635</v>
+        <v>64.08410406075703</v>
       </c>
       <c r="E77">
-        <v>59.638</v>
+        <v>60.44448</v>
       </c>
       <c r="F77">
-        <v>60.486</v>
+        <v>61.29248</v>
       </c>
       <c r="G77">
         <v>23.3</v>
@@ -7601,28 +7601,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M77">
-        <v>4.5848388</v>
+        <v>4.645969984000001</v>
       </c>
       <c r="N77">
-        <v>5.205161199999999</v>
+        <v>5.144030015999999</v>
       </c>
       <c r="O77">
-        <v>1.17116127</v>
+        <v>1.1574067536</v>
       </c>
       <c r="P77">
-        <v>4.033999929999999</v>
+        <v>3.986623262399999</v>
       </c>
       <c r="Q77">
-        <v>5.443999929999999</v>
+        <v>5.396623262399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5310285499205406</v>
+        <v>0.5498782805565515</v>
       </c>
       <c r="T77">
-        <v>3.38322819029226</v>
+        <v>3.51465685432617</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.135298628165509</v>
+        <v>2.107202593584383</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1766169873335724</v>
+        <v>0.1764180871870096</v>
       </c>
       <c r="C78">
-        <v>26.09162406075703</v>
+        <v>25.38272884372648</v>
       </c>
       <c r="D78">
-        <v>64.08410406075703</v>
+        <v>64.18168884372648</v>
       </c>
       <c r="E78">
-        <v>60.44448</v>
+        <v>61.25096</v>
       </c>
       <c r="F78">
-        <v>61.29248</v>
+        <v>62.09896</v>
       </c>
       <c r="G78">
         <v>23.3</v>
@@ -7683,28 +7683,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M78">
-        <v>4.645969984000001</v>
+        <v>4.707101168</v>
       </c>
       <c r="N78">
-        <v>5.144030015999999</v>
+        <v>5.082898831999999</v>
       </c>
       <c r="O78">
-        <v>1.1574067536</v>
+        <v>1.1436522372</v>
       </c>
       <c r="P78">
-        <v>3.986623262399999</v>
+        <v>3.939246594799999</v>
       </c>
       <c r="Q78">
-        <v>5.396623262399999</v>
+        <v>5.349246594799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5498782805565515</v>
+        <v>0.5703671182043896</v>
       </c>
       <c r="T78">
-        <v>3.51465685432617</v>
+        <v>3.657514097841289</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.107202593584383</v>
+        <v>2.079836326135236</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1764180871870096</v>
+        <v>0.1762191870404468</v>
       </c>
       <c r="C79">
-        <v>25.38272884372648</v>
+        <v>24.67413127657514</v>
       </c>
       <c r="D79">
-        <v>64.18168884372648</v>
+        <v>64.27957127657514</v>
       </c>
       <c r="E79">
-        <v>61.25096</v>
+        <v>62.05744</v>
       </c>
       <c r="F79">
-        <v>62.09896</v>
+        <v>62.90544</v>
       </c>
       <c r="G79">
         <v>23.3</v>
@@ -7765,28 +7765,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M79">
-        <v>4.707101168</v>
+        <v>4.768232352</v>
       </c>
       <c r="N79">
-        <v>5.082898831999999</v>
+        <v>5.021767647999999</v>
       </c>
       <c r="O79">
-        <v>1.1436522372</v>
+        <v>1.1298977208</v>
       </c>
       <c r="P79">
-        <v>3.939246594799999</v>
+        <v>3.891869927199999</v>
       </c>
       <c r="Q79">
-        <v>5.349246594799999</v>
+        <v>5.301869927199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5703671182043896</v>
+        <v>0.5927185774565765</v>
       </c>
       <c r="T79">
-        <v>3.657514097841289</v>
+        <v>3.813358363494147</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.079836326135236</v>
+        <v>2.053171757851451</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1762191870404468</v>
+        <v>0.176020286893884</v>
       </c>
       <c r="C80">
-        <v>24.67413127657514</v>
+        <v>23.9658327232058</v>
       </c>
       <c r="D80">
-        <v>64.27957127657514</v>
+        <v>64.3777527232058</v>
       </c>
       <c r="E80">
-        <v>62.05744</v>
+        <v>62.86392</v>
       </c>
       <c r="F80">
-        <v>62.90544</v>
+        <v>63.71192</v>
       </c>
       <c r="G80">
         <v>23.3</v>
@@ -7847,28 +7847,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M80">
-        <v>4.768232352</v>
+        <v>4.829363536000001</v>
       </c>
       <c r="N80">
-        <v>5.021767647999999</v>
+        <v>4.960636463999998</v>
       </c>
       <c r="O80">
-        <v>1.1298977208</v>
+        <v>1.1161432044</v>
       </c>
       <c r="P80">
-        <v>3.891869927199999</v>
+        <v>3.844493259599999</v>
       </c>
       <c r="Q80">
-        <v>5.301869927199999</v>
+        <v>5.254493259599998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5927185774565765</v>
+        <v>0.6171987471137337</v>
       </c>
       <c r="T80">
-        <v>3.813358363494147</v>
+        <v>3.984044940161562</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.053171757851451</v>
+        <v>2.027182241929281</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.176020286893884</v>
+        <v>0.1758213867473213</v>
       </c>
       <c r="C81">
-        <v>23.9658327232058</v>
+        <v>23.25783455586701</v>
       </c>
       <c r="D81">
-        <v>64.3777527232058</v>
+        <v>64.47623455586701</v>
       </c>
       <c r="E81">
-        <v>62.86392</v>
+        <v>63.6704</v>
       </c>
       <c r="F81">
-        <v>63.71192</v>
+        <v>64.5184</v>
       </c>
       <c r="G81">
         <v>23.3</v>
@@ -7929,28 +7929,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M81">
-        <v>4.829363536000001</v>
+        <v>4.89049472</v>
       </c>
       <c r="N81">
-        <v>4.960636463999998</v>
+        <v>4.899505279999999</v>
       </c>
       <c r="O81">
-        <v>1.1161432044</v>
+        <v>1.102388688</v>
       </c>
       <c r="P81">
-        <v>3.844493259599999</v>
+        <v>3.797116591999999</v>
       </c>
       <c r="Q81">
-        <v>5.254493259599998</v>
+        <v>5.207116591999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6171987471137337</v>
+        <v>0.6441269337366066</v>
       </c>
       <c r="T81">
-        <v>3.984044940161562</v>
+        <v>4.17180017449572</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.027182241929281</v>
+        <v>2.001842463905165</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1758213867473213</v>
+        <v>0.1845365366007585</v>
       </c>
       <c r="C82">
-        <v>23.25783455586701</v>
+        <v>18.40108733781771</v>
       </c>
       <c r="D82">
-        <v>64.47623455586701</v>
+        <v>60.42596733781772</v>
       </c>
       <c r="E82">
-        <v>63.6704</v>
+        <v>64.47688000000001</v>
       </c>
       <c r="F82">
-        <v>64.5184</v>
+        <v>65.32488000000001</v>
       </c>
       <c r="G82">
         <v>23.3</v>
@@ -8011,45 +8011,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M82">
-        <v>4.89049472</v>
+        <v>5.879239200000001</v>
       </c>
       <c r="N82">
-        <v>4.899505279999999</v>
+        <v>3.910760799999998</v>
       </c>
       <c r="O82">
-        <v>1.102388688</v>
+        <v>0.8799211799999996</v>
       </c>
       <c r="P82">
-        <v>3.797116591999999</v>
+        <v>3.030839619999999</v>
       </c>
       <c r="Q82">
-        <v>5.207116591999999</v>
+        <v>4.440839619999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6441269337366066</v>
+        <v>0.6738896663197818</v>
       </c>
       <c r="T82">
-        <v>4.17180017449572</v>
+        <v>4.379319117707157</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.225</v>
       </c>
       <c r="W82">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.001842463905165</v>
+        <v>1.665181440482979</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1845365366007585</v>
+        <v>0.1844476864541957</v>
       </c>
       <c r="C83">
-        <v>18.40108733781771</v>
+        <v>17.63333035001841</v>
       </c>
       <c r="D83">
-        <v>60.42596733781772</v>
+        <v>60.46469035001841</v>
       </c>
       <c r="E83">
-        <v>64.47688000000001</v>
+        <v>65.28336</v>
       </c>
       <c r="F83">
-        <v>65.32488000000001</v>
+        <v>66.13136</v>
       </c>
       <c r="G83">
         <v>23.3</v>
@@ -8093,28 +8093,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M83">
-        <v>5.879239200000001</v>
+        <v>5.9518224</v>
       </c>
       <c r="N83">
-        <v>3.910760799999998</v>
+        <v>3.838177599999999</v>
       </c>
       <c r="O83">
-        <v>0.8799211799999996</v>
+        <v>0.8635899599999998</v>
       </c>
       <c r="P83">
-        <v>3.030839619999999</v>
+        <v>2.974587639999999</v>
       </c>
       <c r="Q83">
-        <v>4.440839619999998</v>
+        <v>4.384587639999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6738896663197818</v>
+        <v>0.7069593691899765</v>
       </c>
       <c r="T83">
-        <v>4.379319117707157</v>
+        <v>4.60989572127542</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.665181440482979</v>
+        <v>1.644874349745382</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1844476864541957</v>
+        <v>0.1843588363076329</v>
       </c>
       <c r="C84">
-        <v>17.63333035001841</v>
+        <v>16.86562302408694</v>
       </c>
       <c r="D84">
-        <v>60.46469035001841</v>
+        <v>60.50346302408695</v>
       </c>
       <c r="E84">
-        <v>65.28336</v>
+        <v>66.08984000000001</v>
       </c>
       <c r="F84">
-        <v>66.13136</v>
+        <v>66.93784000000001</v>
       </c>
       <c r="G84">
         <v>23.3</v>
@@ -8175,28 +8175,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M84">
-        <v>5.9518224</v>
+        <v>6.024405600000001</v>
       </c>
       <c r="N84">
-        <v>3.838177599999999</v>
+        <v>3.765594399999999</v>
       </c>
       <c r="O84">
-        <v>0.8635899599999998</v>
+        <v>0.8472587399999997</v>
       </c>
       <c r="P84">
-        <v>2.974587639999999</v>
+        <v>2.918335659999999</v>
       </c>
       <c r="Q84">
-        <v>4.384587639999999</v>
+        <v>4.328335659999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7069593691899765</v>
+        <v>0.7439196253390177</v>
       </c>
       <c r="T84">
-        <v>4.60989572127542</v>
+        <v>4.867598984087008</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.644874349745382</v>
+        <v>1.625056586495437</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1843588363076329</v>
+        <v>0.1842699861610702</v>
       </c>
       <c r="C85">
-        <v>16.86562302408694</v>
+        <v>16.09796545562088</v>
       </c>
       <c r="D85">
-        <v>60.50346302408695</v>
+        <v>60.54228545562088</v>
       </c>
       <c r="E85">
-        <v>66.08984000000001</v>
+        <v>66.89632</v>
       </c>
       <c r="F85">
-        <v>66.93784000000001</v>
+        <v>67.74432</v>
       </c>
       <c r="G85">
         <v>23.3</v>
@@ -8257,28 +8257,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M85">
-        <v>6.024405600000001</v>
+        <v>6.0969888</v>
       </c>
       <c r="N85">
-        <v>3.765594399999999</v>
+        <v>3.693011199999999</v>
       </c>
       <c r="O85">
-        <v>0.8472587399999997</v>
+        <v>0.8309275199999998</v>
       </c>
       <c r="P85">
-        <v>2.918335659999999</v>
+        <v>2.862083679999999</v>
       </c>
       <c r="Q85">
-        <v>4.328335659999999</v>
+        <v>4.27208368</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7439196253390177</v>
+        <v>0.7854999135066891</v>
       </c>
       <c r="T85">
-        <v>4.867598984087008</v>
+        <v>5.157515154750046</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.625056586495437</v>
+        <v>1.605710674751444</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1842699861610702</v>
+        <v>0.1841811360145074</v>
       </c>
       <c r="C86">
-        <v>16.09796545562089</v>
+        <v>15.33035774046334</v>
       </c>
       <c r="D86">
-        <v>60.54228545562088</v>
+        <v>60.58115774046334</v>
       </c>
       <c r="E86">
-        <v>66.89631999999999</v>
+        <v>67.7028</v>
       </c>
       <c r="F86">
-        <v>67.74431999999999</v>
+        <v>68.5508</v>
       </c>
       <c r="G86">
         <v>23.3</v>
@@ -8339,28 +8339,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M86">
-        <v>6.096988799999998</v>
+        <v>6.169572</v>
       </c>
       <c r="N86">
-        <v>3.693011200000001</v>
+        <v>3.620428</v>
       </c>
       <c r="O86">
-        <v>0.8309275200000003</v>
+        <v>0.8145962999999999</v>
       </c>
       <c r="P86">
-        <v>2.86208368</v>
+        <v>2.8058317</v>
       </c>
       <c r="Q86">
-        <v>4.272083680000001</v>
+        <v>4.2158317</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7854999135066887</v>
+        <v>0.8326242400967161</v>
       </c>
       <c r="T86">
-        <v>5.157515154750042</v>
+        <v>5.486086814834817</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.605710674751445</v>
+        <v>1.586819960930839</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1841811360145074</v>
+        <v>0.1840922858679446</v>
       </c>
       <c r="C87">
-        <v>15.33035774046334</v>
+        <v>14.56279997470368</v>
       </c>
       <c r="D87">
-        <v>60.58115774046334</v>
+        <v>60.62007997470367</v>
       </c>
       <c r="E87">
-        <v>67.7028</v>
+        <v>68.50927999999999</v>
       </c>
       <c r="F87">
-        <v>68.5508</v>
+        <v>69.35727999999999</v>
       </c>
       <c r="G87">
         <v>23.3</v>
@@ -8421,28 +8421,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M87">
-        <v>6.169572</v>
+        <v>6.242155199999999</v>
       </c>
       <c r="N87">
-        <v>3.620428</v>
+        <v>3.5478448</v>
       </c>
       <c r="O87">
-        <v>0.8145962999999999</v>
+        <v>0.7982650800000001</v>
       </c>
       <c r="P87">
-        <v>2.8058317</v>
+        <v>2.74957972</v>
       </c>
       <c r="Q87">
-        <v>4.2158317</v>
+        <v>4.15957972</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8326242400967161</v>
+        <v>0.8864806133424616</v>
       </c>
       <c r="T87">
-        <v>5.486086814834817</v>
+        <v>5.86159728350313</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.586819960930839</v>
+        <v>1.568368566036295</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1840922858679446</v>
+        <v>0.1840034357213819</v>
       </c>
       <c r="C88">
-        <v>14.56279997470368</v>
+        <v>13.79529225467836</v>
       </c>
       <c r="D88">
-        <v>60.62007997470367</v>
+        <v>60.65905225467836</v>
       </c>
       <c r="E88">
-        <v>68.50927999999999</v>
+        <v>69.31576</v>
       </c>
       <c r="F88">
-        <v>69.35727999999999</v>
+        <v>70.16376</v>
       </c>
       <c r="G88">
         <v>23.3</v>
@@ -8503,28 +8503,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M88">
-        <v>6.242155199999999</v>
+        <v>6.3147384</v>
       </c>
       <c r="N88">
-        <v>3.5478448</v>
+        <v>3.4752616</v>
       </c>
       <c r="O88">
-        <v>0.7982650800000001</v>
+        <v>0.78193386</v>
       </c>
       <c r="P88">
-        <v>2.74957972</v>
+        <v>2.69332774</v>
       </c>
       <c r="Q88">
-        <v>4.15957972</v>
+        <v>4.103327739999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8864806133424616</v>
+        <v>0.9486225824721684</v>
       </c>
       <c r="T88">
-        <v>5.86159728350313</v>
+        <v>6.294878593505032</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.568368566036295</v>
+        <v>1.550341341139326</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1840034357213819</v>
+        <v>0.1839145855748191</v>
       </c>
       <c r="C89">
-        <v>13.79529225467836</v>
+        <v>13.02783467697182</v>
       </c>
       <c r="D89">
-        <v>60.65905225467836</v>
+        <v>60.69807467697183</v>
       </c>
       <c r="E89">
-        <v>69.31576</v>
+        <v>70.12224000000001</v>
       </c>
       <c r="F89">
-        <v>70.16376</v>
+        <v>70.97024</v>
       </c>
       <c r="G89">
         <v>23.3</v>
@@ -8585,28 +8585,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M89">
-        <v>6.3147384</v>
+        <v>6.3873216</v>
       </c>
       <c r="N89">
-        <v>3.4752616</v>
+        <v>3.402678399999999</v>
       </c>
       <c r="O89">
-        <v>0.78193386</v>
+        <v>0.7656026399999999</v>
       </c>
       <c r="P89">
-        <v>2.69332774</v>
+        <v>2.637075759999999</v>
       </c>
       <c r="Q89">
-        <v>4.103327739999999</v>
+        <v>4.047075759999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9486225824721684</v>
+        <v>1.021121546456826</v>
       </c>
       <c r="T89">
-        <v>6.294878593505032</v>
+        <v>6.800373455173916</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.550341341139326</v>
+        <v>1.532723825899106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1839145855748191</v>
+        <v>0.1838257354282563</v>
       </c>
       <c r="C90">
-        <v>13.02783467697182</v>
+        <v>12.26042733841713</v>
       </c>
       <c r="D90">
-        <v>60.69807467697183</v>
+        <v>60.73714733841712</v>
       </c>
       <c r="E90">
-        <v>70.12224000000001</v>
+        <v>70.92872</v>
       </c>
       <c r="F90">
-        <v>70.97024</v>
+        <v>71.77672</v>
       </c>
       <c r="G90">
         <v>23.3</v>
@@ -8667,28 +8667,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M90">
-        <v>6.3873216</v>
+        <v>6.459904799999999</v>
       </c>
       <c r="N90">
-        <v>3.402678399999999</v>
+        <v>3.3300952</v>
       </c>
       <c r="O90">
-        <v>0.7656026399999999</v>
+        <v>0.7492714199999999</v>
       </c>
       <c r="P90">
-        <v>2.637075759999999</v>
+        <v>2.58082378</v>
       </c>
       <c r="Q90">
-        <v>4.047075759999999</v>
+        <v>3.99082378</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.021121546456826</v>
+        <v>1.106802140256876</v>
       </c>
       <c r="T90">
-        <v>6.800373455173916</v>
+        <v>7.39777647350987</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.532723825899106</v>
+        <v>1.515502209877768</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1838257354282563</v>
+        <v>0.2281683584264023</v>
       </c>
       <c r="C91">
-        <v>12.26042733841713</v>
+        <v>-3.314208988971103</v>
       </c>
       <c r="D91">
-        <v>60.73714733841712</v>
+        <v>45.9689910110289</v>
       </c>
       <c r="E91">
-        <v>70.92872</v>
+        <v>71.73520000000001</v>
       </c>
       <c r="F91">
-        <v>71.77672</v>
+        <v>72.58320000000001</v>
       </c>
       <c r="G91">
         <v>23.3</v>
@@ -8749,45 +8749,45 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M91">
-        <v>6.459904799999999</v>
+        <v>10.65521376</v>
       </c>
       <c r="N91">
-        <v>3.3300952</v>
+        <v>-0.8652137600000032</v>
       </c>
       <c r="O91">
-        <v>0.7492714199999999</v>
+        <v>-0.1946730960000007</v>
       </c>
       <c r="P91">
-        <v>2.58082378</v>
+        <v>-0.6705406640000025</v>
       </c>
       <c r="Q91">
-        <v>3.99082378</v>
+        <v>0.7394593359999977</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.106802140256876</v>
+        <v>1.233614970039244</v>
       </c>
       <c r="T91">
-        <v>7.39777647350987</v>
+        <v>8.281971644384914</v>
       </c>
       <c r="U91">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.225</v>
+        <v>0.2067297803324407</v>
       </c>
       <c r="W91">
-        <v>0.06974999999999999</v>
+        <v>0.1164520682471977</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.515502209877768</v>
+        <v>0.9187990236997363</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2281683584264023</v>
+        <v>0.2291783584264024</v>
       </c>
       <c r="C92">
-        <v>-3.314208988971103</v>
+        <v>-4.373874159345363</v>
       </c>
       <c r="D92">
-        <v>45.9689910110289</v>
+        <v>45.71580584065464</v>
       </c>
       <c r="E92">
-        <v>71.73520000000001</v>
+        <v>72.54168</v>
       </c>
       <c r="F92">
-        <v>72.58320000000001</v>
+        <v>73.38968</v>
       </c>
       <c r="G92">
         <v>23.3</v>
@@ -8831,37 +8831,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M92">
-        <v>10.65521376</v>
+        <v>10.773605024</v>
       </c>
       <c r="N92">
-        <v>-0.8652137600000032</v>
+        <v>-0.9836050240000009</v>
       </c>
       <c r="O92">
-        <v>-0.1946730960000007</v>
+        <v>-0.2213111304000002</v>
       </c>
       <c r="P92">
-        <v>-0.6705406640000025</v>
+        <v>-0.7622938936000008</v>
       </c>
       <c r="Q92">
-        <v>0.7394593359999977</v>
+        <v>0.6477061063999994</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.233614970039244</v>
+        <v>1.365594411154716</v>
       </c>
       <c r="T92">
-        <v>8.281971644384914</v>
+        <v>9.202190715983241</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2067297803324407</v>
+        <v>0.2044580245046117</v>
       </c>
       <c r="W92">
-        <v>0.1164520682471977</v>
+        <v>0.116785562002723</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9187990236997363</v>
+        <v>0.9087023311316076</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2291783584264024</v>
+        <v>0.2301883584264024</v>
       </c>
       <c r="C93">
-        <v>-4.373874159345363</v>
+        <v>-5.430765651117994</v>
       </c>
       <c r="D93">
-        <v>45.71580584065464</v>
+        <v>45.46539434888201</v>
       </c>
       <c r="E93">
-        <v>72.54168</v>
+        <v>73.34816000000001</v>
       </c>
       <c r="F93">
-        <v>73.38968</v>
+        <v>74.19616000000001</v>
       </c>
       <c r="G93">
         <v>23.3</v>
@@ -8913,37 +8913,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M93">
-        <v>10.773605024</v>
+        <v>10.891996288</v>
       </c>
       <c r="N93">
-        <v>-0.9836050240000009</v>
+        <v>-1.101996288000002</v>
       </c>
       <c r="O93">
-        <v>-0.2213111304000002</v>
+        <v>-0.2479491648000005</v>
       </c>
       <c r="P93">
-        <v>-0.7622938936000008</v>
+        <v>-0.8540471232000018</v>
       </c>
       <c r="Q93">
-        <v>0.6477061063999994</v>
+        <v>0.5559528767999984</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.365594411154716</v>
+        <v>1.530568712549056</v>
       </c>
       <c r="T93">
-        <v>9.202190715983241</v>
+        <v>10.35246455548115</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2044580245046117</v>
+        <v>0.2022356546730398</v>
       </c>
       <c r="W93">
-        <v>0.116785562002723</v>
+        <v>0.1171118058939978</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9087023311316076</v>
+        <v>0.898825131880177</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2301883584264024</v>
+        <v>0.2311983584264024</v>
       </c>
       <c r="C94">
-        <v>-5.430765651117994</v>
+        <v>-6.484928795036438</v>
       </c>
       <c r="D94">
-        <v>45.46539434888201</v>
+        <v>45.21771120496356</v>
       </c>
       <c r="E94">
-        <v>73.34816000000001</v>
+        <v>74.15464</v>
       </c>
       <c r="F94">
-        <v>74.19616000000001</v>
+        <v>75.00264</v>
       </c>
       <c r="G94">
         <v>23.3</v>
@@ -8995,37 +8995,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M94">
-        <v>10.891996288</v>
+        <v>11.010387552</v>
       </c>
       <c r="N94">
-        <v>-1.101996288000002</v>
+        <v>-1.220387552000002</v>
       </c>
       <c r="O94">
-        <v>-0.2479491648000005</v>
+        <v>-0.2745871992000004</v>
       </c>
       <c r="P94">
-        <v>-0.8540471232000018</v>
+        <v>-0.9458003528000014</v>
       </c>
       <c r="Q94">
-        <v>0.5559528767999984</v>
+        <v>0.4641996471999987</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.530568712549056</v>
+        <v>1.742678528627493</v>
       </c>
       <c r="T94">
-        <v>10.35246455548115</v>
+        <v>11.83138806340703</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2022356546730398</v>
+        <v>0.2000610777410717</v>
       </c>
       <c r="W94">
-        <v>0.1171118058939978</v>
+        <v>0.1174310337876107</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.898825131880177</v>
+        <v>0.889160345515874</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2311983584264024</v>
+        <v>0.2322083584264024</v>
       </c>
       <c r="C95">
-        <v>-6.484928795036438</v>
+        <v>-7.536407939401769</v>
       </c>
       <c r="D95">
-        <v>45.21771120496356</v>
+        <v>44.97271206059824</v>
       </c>
       <c r="E95">
-        <v>74.15464</v>
+        <v>74.96112000000001</v>
       </c>
       <c r="F95">
-        <v>75.00264</v>
+        <v>75.80912000000001</v>
       </c>
       <c r="G95">
         <v>23.3</v>
@@ -9077,37 +9077,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M95">
-        <v>11.010387552</v>
+        <v>11.128778816</v>
       </c>
       <c r="N95">
-        <v>-1.220387552000002</v>
+        <v>-1.338778816000003</v>
       </c>
       <c r="O95">
-        <v>-0.2745871992000004</v>
+        <v>-0.3012252336000007</v>
       </c>
       <c r="P95">
-        <v>-0.9458003528000014</v>
+        <v>-1.037553582400002</v>
       </c>
       <c r="Q95">
-        <v>0.4641996471999987</v>
+        <v>0.3724464175999977</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.742678528627493</v>
+        <v>2.025491616732075</v>
       </c>
       <c r="T95">
-        <v>11.83138806340703</v>
+        <v>13.80328607397487</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2000610777410717</v>
+        <v>0.1979327684034007</v>
       </c>
       <c r="W95">
-        <v>0.1174310337876107</v>
+        <v>0.1177434695983808</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.889160345515874</v>
+        <v>0.8797011929040029</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2322083584264024</v>
+        <v>0.2332183584264024</v>
       </c>
       <c r="C96">
-        <v>-7.536407939401769</v>
+        <v>-8.585246476540703</v>
       </c>
       <c r="D96">
-        <v>44.97271206059824</v>
+        <v>44.7303535234593</v>
       </c>
       <c r="E96">
-        <v>74.96112000000001</v>
+        <v>75.7676</v>
       </c>
       <c r="F96">
-        <v>75.80912000000001</v>
+        <v>76.6156</v>
       </c>
       <c r="G96">
         <v>23.3</v>
@@ -9159,37 +9159,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M96">
-        <v>11.128778816</v>
+        <v>11.24717008</v>
       </c>
       <c r="N96">
-        <v>-1.338778816000003</v>
+        <v>-1.457170080000003</v>
       </c>
       <c r="O96">
-        <v>-0.3012252336000007</v>
+        <v>-0.3278632680000006</v>
       </c>
       <c r="P96">
-        <v>-1.037553582400002</v>
+        <v>-1.129306812000002</v>
       </c>
       <c r="Q96">
-        <v>0.3724464175999977</v>
+        <v>0.2806931879999981</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.025491616732075</v>
+        <v>2.421429940078491</v>
       </c>
       <c r="T96">
-        <v>13.80328607397487</v>
+        <v>16.56394328876985</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1979327684034007</v>
+        <v>0.1958492655781017</v>
       </c>
       <c r="W96">
-        <v>0.1177434695983808</v>
+        <v>0.1180493278131347</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8797011929040029</v>
+        <v>0.8704411803471187</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2332183584264024</v>
+        <v>0.2342283584264023</v>
       </c>
       <c r="C97">
-        <v>-8.585246476540703</v>
+        <v>-9.631486868426407</v>
       </c>
       <c r="D97">
-        <v>44.7303535234593</v>
+        <v>44.4905931315736</v>
       </c>
       <c r="E97">
-        <v>75.7676</v>
+        <v>76.57408000000001</v>
       </c>
       <c r="F97">
-        <v>76.6156</v>
+        <v>77.42208000000001</v>
       </c>
       <c r="G97">
         <v>23.3</v>
@@ -9241,37 +9241,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M97">
-        <v>11.24717008</v>
+        <v>11.365561344</v>
       </c>
       <c r="N97">
-        <v>-1.457170080000003</v>
+        <v>-1.575561344000002</v>
       </c>
       <c r="O97">
-        <v>-0.3278632680000006</v>
+        <v>-0.3545013024000005</v>
       </c>
       <c r="P97">
-        <v>-1.129306812000002</v>
+        <v>-1.221060041600002</v>
       </c>
       <c r="Q97">
-        <v>0.2806931879999981</v>
+        <v>0.1889399583999984</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.421429940078491</v>
+        <v>3.015337425098115</v>
       </c>
       <c r="T97">
-        <v>16.56394328876985</v>
+        <v>20.70492911096232</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1958492655781017</v>
+        <v>0.1938091690616632</v>
       </c>
       <c r="W97">
-        <v>0.1180493278131347</v>
+        <v>0.1183488139817478</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8704411803471187</v>
+        <v>0.861374084718503</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2342283584264023</v>
+        <v>0.2352383584264024</v>
       </c>
       <c r="C98">
-        <v>-9.631486868426393</v>
+        <v>-10.67517067147955</v>
       </c>
       <c r="D98">
-        <v>44.4905931315736</v>
+        <v>44.25338932852043</v>
       </c>
       <c r="E98">
-        <v>76.57408</v>
+        <v>77.38055999999999</v>
       </c>
       <c r="F98">
-        <v>77.42207999999999</v>
+        <v>78.22855999999999</v>
       </c>
       <c r="G98">
         <v>23.3</v>
@@ -9323,37 +9323,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M98">
-        <v>11.365561344</v>
+        <v>11.483952608</v>
       </c>
       <c r="N98">
-        <v>-1.575561344</v>
+        <v>-1.693952608</v>
       </c>
       <c r="O98">
-        <v>-0.3545013024000001</v>
+        <v>-0.3811393368</v>
       </c>
       <c r="P98">
-        <v>-1.2210600416</v>
+        <v>-1.3128132712</v>
       </c>
       <c r="Q98">
-        <v>0.1889399583999998</v>
+        <v>0.09718672880000012</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.015337425098108</v>
+        <v>4.005183233464145</v>
       </c>
       <c r="T98">
-        <v>20.70492911096227</v>
+        <v>27.60657214794969</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1938091690616632</v>
+        <v>0.1918111363909244</v>
       </c>
       <c r="W98">
-        <v>0.1183488139817478</v>
+        <v>0.1186421251778123</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8613740847185031</v>
+        <v>0.8524939395152196</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2352383584264024</v>
+        <v>0.2362483584264023</v>
       </c>
       <c r="C99">
-        <v>-10.67517067147955</v>
+        <v>-11.71633856058035</v>
       </c>
       <c r="D99">
-        <v>44.25338932852043</v>
+        <v>44.01870143941964</v>
       </c>
       <c r="E99">
-        <v>77.38055999999999</v>
+        <v>78.18704</v>
       </c>
       <c r="F99">
-        <v>78.22855999999999</v>
+        <v>79.03504</v>
       </c>
       <c r="G99">
         <v>23.3</v>
@@ -9405,37 +9405,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M99">
-        <v>11.483952608</v>
+        <v>11.602343872</v>
       </c>
       <c r="N99">
-        <v>-1.693952608</v>
+        <v>-1.812343872000001</v>
       </c>
       <c r="O99">
-        <v>-0.3811393368</v>
+        <v>-0.4077773712000003</v>
       </c>
       <c r="P99">
-        <v>-1.3128132712</v>
+        <v>-1.404566500800001</v>
       </c>
       <c r="Q99">
-        <v>0.09718672880000012</v>
+        <v>0.005433499199999137</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.005183233464145</v>
+        <v>5.984874850196216</v>
       </c>
       <c r="T99">
-        <v>27.60657214794969</v>
+        <v>41.40985822192454</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1918111363909244</v>
+        <v>0.1898538798971394</v>
       </c>
       <c r="W99">
-        <v>0.1186421251778123</v>
+        <v>0.1189294504310999</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8524939395152196</v>
+        <v>0.8437950217650642</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2362483584264023</v>
+        <v>0.2372583584264024</v>
       </c>
       <c r="C100">
-        <v>-11.71633856058035</v>
+        <v>-12.75503035232045</v>
       </c>
       <c r="D100">
-        <v>44.01870143941964</v>
+        <v>43.78648964767954</v>
       </c>
       <c r="E100">
-        <v>78.18704</v>
+        <v>78.99351999999999</v>
       </c>
       <c r="F100">
-        <v>79.03504</v>
+        <v>79.84151999999999</v>
       </c>
       <c r="G100">
         <v>23.3</v>
@@ -9487,37 +9487,37 @@
         <v>9.789999999999999</v>
       </c>
       <c r="M100">
-        <v>11.602343872</v>
+        <v>11.720735136</v>
       </c>
       <c r="N100">
-        <v>-1.812343872000001</v>
+        <v>-1.930735136000001</v>
       </c>
       <c r="O100">
-        <v>-0.4077773712000003</v>
+        <v>-0.4344154056000002</v>
       </c>
       <c r="P100">
-        <v>-1.404566500800001</v>
+        <v>-1.496319730400001</v>
       </c>
       <c r="Q100">
-        <v>0.005433499199999137</v>
+        <v>-0.08631973040000052</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.984874850196216</v>
+        <v>11.92394970039243</v>
       </c>
       <c r="T100">
-        <v>41.40985822192454</v>
+        <v>82.81971644384906</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1898538798971394</v>
+        <v>0.1879361639385825</v>
       </c>
       <c r="W100">
-        <v>0.1189294504310999</v>
+        <v>0.1192109711338161</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8437950217650642</v>
+        <v>0.8352718397270332</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2372583584264024</v>
-      </c>
-      <c r="C101">
-        <v>-12.75503035232045</v>
-      </c>
-      <c r="D101">
-        <v>43.78648964767954</v>
-      </c>
-      <c r="E101">
-        <v>78.99351999999999</v>
-      </c>
-      <c r="F101">
-        <v>79.84151999999999</v>
-      </c>
-      <c r="G101">
-        <v>23.3</v>
-      </c>
-      <c r="H101">
-        <v>79.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.2</v>
-      </c>
-      <c r="K101">
-        <v>1.41</v>
-      </c>
-      <c r="L101">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="M101">
-        <v>11.720735136</v>
-      </c>
-      <c r="N101">
-        <v>-1.930735136000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.4344154056000002</v>
-      </c>
-      <c r="P101">
-        <v>-1.496319730400001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.08631973040000052</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.92394970039243</v>
-      </c>
-      <c r="T101">
-        <v>82.81971644384906</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1879361639385825</v>
-      </c>
-      <c r="W101">
-        <v>0.1192109711338161</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8352718397270332</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
